--- a/docs/xlsx/jobs-2026-08-19.xlsx
+++ b/docs/xlsx/jobs-2026-08-19.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="291">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1341" uniqueCount="876">
   <si>
     <t>Title</t>
   </si>
@@ -418,6 +418,48 @@
     <t>https://www.conservationjobboard.com/job-listing-water-resource-control-engineer-sacramento-california/4880196537</t>
   </si>
   <si>
+    <t>BayREN Codes &amp; Standards Lead</t>
+  </si>
+  <si>
+    <t>Metropolitan Transportation Commission (MTC)</t>
+  </si>
+  <si>
+    <t>San Francisco, California, United States</t>
+  </si>
+  <si>
+    <t>Full-Time</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Transportation</t>
+  </si>
+  <si>
+    <t>https://greenjobs.greenjobsearch.org/jobs/bayren-codes-standards-lead/</t>
+  </si>
+  <si>
+    <t>Accountant (Hybrid, Oakland CA)</t>
+  </si>
+  <si>
+    <t>National Center for Youth Law (NCYL)</t>
+  </si>
+  <si>
+    <t>Oakland, California</t>
+  </si>
+  <si>
+    <t>Full Time</t>
+  </si>
+  <si>
+    <t>USD 67500.00 - 76500.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Human Rights Civil Liberties, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/52686ee816fc4a5ab27224f05112be56-accountant-hybrid-oakland-ca-national-center-for-youth-law-ncyl-oakland</t>
+  </si>
+  <si>
     <t>Administrative Coordinator</t>
   </si>
   <si>
@@ -427,9 +469,6 @@
     <t>ATLANTA, Georgia</t>
   </si>
   <si>
-    <t>Full Time</t>
-  </si>
-  <si>
     <t>USD 17.00 - 17.00/hour</t>
   </si>
   <si>
@@ -439,6 +478,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/d3f2b4dfb1e74e3e9bfc55661264b207-administrative-coordinator-lifecycle-building-center-inc-atlanta</t>
   </si>
   <si>
+    <t>Washington Conservation Action</t>
+  </si>
+  <si>
+    <t>Seattle, Washington</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 65000.00/year</t>
+  </si>
+  <si>
+    <t>Climate Change, Environment, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/25ba4183f2404bd68966fed28566fdce-administrative-coordinator-washington-conservation-action-seattle</t>
+  </si>
+  <si>
     <t>Administrative Coordinator (part-time)</t>
   </si>
   <si>
@@ -451,15 +505,60 @@
     <t>Part Time</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>Children Youth, Education, Environment</t>
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/0b059a5b7f814c2abb31aea890ca3a74-administrative-coordinator-part-time-wild-earth-wilderness-school-high-falls</t>
   </si>
   <si>
+    <t>Agente de acompanhamento (masculino)</t>
+  </si>
+  <si>
+    <t>Se Mudando</t>
+  </si>
+  <si>
+    <t>São Carlos, São Paulo, BR</t>
+  </si>
+  <si>
+    <t>Contract</t>
+  </si>
+  <si>
+    <t>Community Development, Policy, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f9ae6cd8de204aa6b5ba1754fd79e711-agente-de-acompanhamento-masculino-se-mudando-sao-carlos</t>
+  </si>
+  <si>
+    <t>Associate Director of Policy Implementation</t>
+  </si>
+  <si>
+    <t>NYC Campaign Finance Board</t>
+  </si>
+  <si>
+    <t>New York, New York</t>
+  </si>
+  <si>
+    <t>USD 125000.00 - 135000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/eb50adbff88a492599ba5059171a3561-associate-director-of-policy-implementation-nyc-campaign-finance-board-new-york</t>
+  </si>
+  <si>
+    <t>Become a Campaign Organizer in Iowa!</t>
+  </si>
+  <si>
+    <t>The Outreach Team</t>
+  </si>
+  <si>
+    <t>Waterloo, Iowa</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 67000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/7845520e0453475fb572aaf5edd3124b-become-a-campaign-organizer-in-iowa-the-outreach-team-waterloo</t>
+  </si>
+  <si>
     <t>Bilingual Intake Specialist</t>
   </si>
   <si>
@@ -496,6 +595,51 @@
     <t>https://www.idealist.org/en/nonprofit-job/bb27ea1795834715adfb4f5bf6b32150-building-facilities-manager-council-of-peoples-organization-kings-county</t>
   </si>
   <si>
+    <t>Business Development Representative</t>
+  </si>
+  <si>
+    <t>NATIONAL CONFLICT RESOLUTION CENTER</t>
+  </si>
+  <si>
+    <t>San Diego, California</t>
+  </si>
+  <si>
+    <t>USD 29.00 - 33.00/hour</t>
+  </si>
+  <si>
+    <t>Conflict Resolution</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6a477e1dea8e409bb7f1295f89fd704e-business-development-representative-national-conflict-resolution-center-san-diego</t>
+  </si>
+  <si>
+    <t>Canvasser</t>
+  </si>
+  <si>
+    <t>Make the Road Action</t>
+  </si>
+  <si>
+    <t>Las Vegas, Nevada</t>
+  </si>
+  <si>
+    <t>Part Time, Temporary</t>
+  </si>
+  <si>
+    <t>USD 25.00 - 25.00/hour</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Immigrants Or Refugees, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d419d1bf8e2440529620ac295c3b5547-canvasser-make-the-road-action-las-vegas</t>
+  </si>
+  <si>
+    <t>Canvasser Lead</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/064b644fa8b84891acc8327c7e7efd14-canvasser-lead-make-the-road-action-las-vegas</t>
+  </si>
+  <si>
     <t>Captador/a de Fondos en vía pública - Córdoba (Capital)</t>
   </si>
   <si>
@@ -550,6 +694,33 @@
     <t>https://www.idealist.org/en/nonprofit-job/cd6790cd730341a0bdfc21cce664eec4-case-manager-vocational-esl-instructor-ace-association-of-community-employment-programs-for-the-homeless-inc-queens-county</t>
   </si>
   <si>
+    <t>Chief Deputy Attorney General Social Justice Division (3904)</t>
+  </si>
+  <si>
+    <t>New York State Office of the Attorney General</t>
+  </si>
+  <si>
+    <t>USD 243880.00 - 243880.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/government-job/3432b445b8d641a2abd84c2682cbc9ff-chief-deputy-attorney-general-social-justice-division-3904-new-york-state-office-of-the-attorney-general-new-york</t>
+  </si>
+  <si>
+    <t>Chief External Affairs and Programs Officer</t>
+  </si>
+  <si>
+    <t>Planned Parenthood of Greater New York</t>
+  </si>
+  <si>
+    <t>Brooklyn, New York</t>
+  </si>
+  <si>
+    <t>USD 285000.00 - 305000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/84f4f5c95aa2476bbeb662c9f2725cd8-chief-external-affairs-and-programs-officer-planned-parenthood-of-greater-new-york-brooklyn</t>
+  </si>
+  <si>
     <t>Chief Financial Officer/Corporate Treasurer</t>
   </si>
   <si>
@@ -565,6 +736,102 @@
     <t>https://www.idealist.org/en/nonprofit-job/800bd8c71a0e4d619b40a217cdcf51ca-chief-financial-officercorporate-treasurer-warren-whitney-management-consulting-charlottesville</t>
   </si>
   <si>
+    <t>Civic Leadership Facilitator (Part-time/Temporary)</t>
+  </si>
+  <si>
+    <t>RF CUNY (Institute for Justice and Opportunity)</t>
+  </si>
+  <si>
+    <t>USD 6500.00 - 6500.00/year</t>
+  </si>
+  <si>
+    <t>Prison Reform, Education, Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e9ad16a9b32d420eaf3c7e846ac98898-civic-leadership-facilitator-part-timetemporary-rf-cuny-institute-for-justice-and-opportunity-new-york</t>
+  </si>
+  <si>
+    <t>Communications Associate</t>
+  </si>
+  <si>
+    <t>Essential Partners</t>
+  </si>
+  <si>
+    <t>Remote</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Community Development, Conflict Resolution</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/58c11565ae834efbaa3b1094298f3e09-communications-associate-essential-partners-cambridge</t>
+  </si>
+  <si>
+    <t>Communications Associate (FTE)</t>
+  </si>
+  <si>
+    <t>Black Farmer Fund</t>
+  </si>
+  <si>
+    <t>USD 61800.00 - 74675.00/year</t>
+  </si>
+  <si>
+    <t>Agriculture, Economic Development, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d8093edb80ab462c908e0e64ac9ca53c-communications-associate-fte-black-farmer-fund-new-york</t>
+  </si>
+  <si>
+    <t>Communications Associate- Economic Growth Center (EGC)</t>
+  </si>
+  <si>
+    <t>Yale University</t>
+  </si>
+  <si>
+    <t>New Haven, Connecticut</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/f9d9960fb8b249caa96f46bc389696d8-communications-associate-economic-growth-center-egc-yale-university-new-haven</t>
+  </si>
+  <si>
+    <t>Communications Director, REBUILD.US</t>
+  </si>
+  <si>
+    <t>Assets Under Movement</t>
+  </si>
+  <si>
+    <t>Washington, DC, District of Columbia</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8708092225bb4a59b94f896b790c6c6c-communications-director-rebuildus-assets-under-movement-washington-dc</t>
+  </si>
+  <si>
+    <t>Communications Manager</t>
+  </si>
+  <si>
+    <t>USD 105000.00 - 130000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9d57c10339d44563a0e33e629ac1be8a-communications-manager-national-center-for-youth-law-ncyl-oakland</t>
+  </si>
+  <si>
+    <t>Computational Social Scientist</t>
+  </si>
+  <si>
+    <t>GoodPower</t>
+  </si>
+  <si>
+    <t>USD 120000.00 - 140000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Community Development, Energy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5bdb274a5f374885a9ab42ea824c2903-computational-social-scientist-goodpower-boston</t>
+  </si>
+  <si>
     <t>Coordinador/a Territorial Programa de Fortalecimiento y Desarrollo de Cadenas Productivas - TARTAGAL</t>
   </si>
   <si>
@@ -577,6 +844,18 @@
     <t>https://www.idealist.org/en/nonprofit-job/acdbf64ac3eb4ba3bd9f49db8f0e2ba7-coordinadora-territorial-programa-de-fortalecimiento-y-desarrollo-de-cadenas-productivas-tartagal-asociacion-civil-pata-pila-tartagal</t>
   </si>
   <si>
+    <t>CRM Coordinator &amp; Systems Support</t>
+  </si>
+  <si>
+    <t>Morristown, New Jersey</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 72000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/fa741272b21a4fcbbb6d821590d2ab51-crm-coordinator-systems-support-morristown</t>
+  </si>
+  <si>
     <t>Cuidadoras/es Sociales para el programa de Córdoba</t>
   </si>
   <si>
@@ -610,6 +889,69 @@
     <t>https://www.idealist.org/en/nonprofit-job/ea8a88db6ca54d489598a88f657c62a4-cuidadorases-sociales-para-el-programa-de-obera-aldeas-infantiles-sos-argentina-obera</t>
   </si>
   <si>
+    <t>Data &amp; Administrative Coordinator</t>
+  </si>
+  <si>
+    <t>SAADA</t>
+  </si>
+  <si>
+    <t>Philadelphia, Pennsylvania</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 65000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Immigrants Or Refugees, Race Ethnicity</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e6f71eaf3d724ecda22a1889cd772311-data-administrative-coordinator-saada-philadelphia</t>
+  </si>
+  <si>
+    <t>Deputy Executive Director (DED)</t>
+  </si>
+  <si>
+    <t>People With Disabilities Foundation</t>
+  </si>
+  <si>
+    <t>San Francisco, California</t>
+  </si>
+  <si>
+    <t>USD 78000.00 - 82000.00/year</t>
+  </si>
+  <si>
+    <t>Disability, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d289401955fb4db7ab8bd24df587db47-deputy-executive-director-ded-people-with-disabilities-foundation-san-francisco</t>
+  </si>
+  <si>
+    <t>Desarrollo de fondos</t>
+  </si>
+  <si>
+    <t>Fundación Banco de Alimentos Córdoba</t>
+  </si>
+  <si>
+    <t>Hunger Food Security</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/fb662b917c394587be972772147cea98-desarrollo-de-fondos-fundacion-banco-de-alimentos-cordoba-cordoba</t>
+  </si>
+  <si>
+    <t>Development Assistant</t>
+  </si>
+  <si>
+    <t>Tipping Point Community</t>
+  </si>
+  <si>
+    <t>USD 73057.00 - 73057.00/year</t>
+  </si>
+  <si>
+    <t>Philanthropy, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5f7bd687367945c5bed0f4d8fac8f27e-development-assistant-tipping-point-community-san-francisco</t>
+  </si>
+  <si>
     <t>Development Associate or Assistant (Dependent on experience)</t>
   </si>
   <si>
@@ -628,6 +970,141 @@
     <t>https://www.idealist.org/en/nonprofit-job/5691e8ef6713487ea5f181b434e742ce-development-associate-or-assistant-dependent-on-experience-cambridge-in-america-new-york</t>
   </si>
   <si>
+    <t>Development Director, NYC</t>
+  </si>
+  <si>
+    <t>Reading Partners</t>
+  </si>
+  <si>
+    <t>USD 98007.00 - 122508.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Civic Engagement, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c568e8e4b7414ed8af250a172fae79bf-development-director-nyc-reading-partners-new-york</t>
+  </si>
+  <si>
+    <t>Development Manager</t>
+  </si>
+  <si>
+    <t>BOUNCE CHILDRENS FOUNDATION</t>
+  </si>
+  <si>
+    <t>Wheeling, Illinois</t>
+  </si>
+  <si>
+    <t>USD 52000.00 - 56000.00/year</t>
+  </si>
+  <si>
+    <t>Disability, Health Medicine, Volunteering</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ee562b3ddfb24e938eb89bc2b822da02-development-manager-bounce-childrens-foundation-wheeling</t>
+  </si>
+  <si>
+    <t>Depression and Bipolar Support Alliance</t>
+  </si>
+  <si>
+    <t>Chicago, Illinois</t>
+  </si>
+  <si>
+    <t>USD 76000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d35e2624148c493d803c146b36fb7552-development-manager-depression-and-bipolar-support-alliance-chicago</t>
+  </si>
+  <si>
+    <t>Development Manager - Special Events</t>
+  </si>
+  <si>
+    <t>Ronald McDonald House Charities of Western Washington and Alaska</t>
+  </si>
+  <si>
+    <t>Seattle, WA</t>
+  </si>
+  <si>
+    <t>USD 82400.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d4437e18a2634de7a80fe18ac6b496bd-development-manager-special-events-ronald-mcdonald-house-charities-of-western-washington-and-alaska-seattle</t>
+  </si>
+  <si>
+    <t>Development Operations Manager</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3434633ff551457ebf045481ad5b3f1d-development-operations-manager-national-conflict-resolution-center-san-diego</t>
+  </si>
+  <si>
+    <t>Development Operations Manager, National Development</t>
+  </si>
+  <si>
+    <t>USD 71353.00 - 83945.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/14083c3f893e463dad4fd7765ede861b-development-operations-manager-national-development-reading-partners-oakland</t>
+  </si>
+  <si>
+    <t>Development Operations Specialist</t>
+  </si>
+  <si>
+    <t>The Brookline Center for Community Mental Health</t>
+  </si>
+  <si>
+    <t>Brookline, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 63000.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine, Mental Health, Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ed9a973973914d60874009db7613a5b0-development-operations-specialist-the-brookline-center-for-community-mental-health-brookline</t>
+  </si>
+  <si>
+    <t>Digital Communications Organizer</t>
+  </si>
+  <si>
+    <t>League of Women Voters of Pennsylvania</t>
+  </si>
+  <si>
+    <t>Remote (Pennsylvania)</t>
+  </si>
+  <si>
+    <t>USD 28.00 - 32.00/hour</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Policy, Women</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/021ee71964ff495da512238fb5f48c6e-digital-communications-organizer-league-of-women-voters-of-pennsylvania-harrisburg</t>
+  </si>
+  <si>
+    <t>Digital Fundraising Manager</t>
+  </si>
+  <si>
+    <t>Brady United Against Gun Violence</t>
+  </si>
+  <si>
+    <t>Washington, District of Columbia</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Conflict Resolution, Crime Safety</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/873857175db7430a8adfaf45d015055f-digital-fundraising-manager-brady-united-against-gun-violence-washington</t>
+  </si>
+  <si>
     <t>Digital Marketing Associate</t>
   </si>
   <si>
@@ -646,15 +1123,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/362d9d35726a4f16a2ceac41fd8d6a04-digital-marketing-associate-defenders-of-wildlife-washington</t>
   </si>
   <si>
+    <t>Directing Attorney (Temporary)</t>
+  </si>
+  <si>
+    <t>Full Time, Temporary</t>
+  </si>
+  <si>
+    <t>USD 126700.00 - 142000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c6a94223148b4a909340708e798ee058-directing-attorney-temporary-national-center-for-youth-law-ncyl-oakland</t>
+  </si>
+  <si>
     <t>Director of Development</t>
   </si>
   <si>
     <t>Mamatoto Village</t>
   </si>
   <si>
-    <t>Washington, District of Columbia</t>
-  </si>
-  <si>
     <t>USD 130000.00 - 150000.00/year</t>
   </si>
   <si>
@@ -664,6 +1150,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/9f3e87dddab947a796891957d4281ee5-director-of-development-mamatoto-village-washington</t>
   </si>
   <si>
+    <t>Director of Finance</t>
+  </si>
+  <si>
+    <t>The Century Foundation</t>
+  </si>
+  <si>
+    <t>USD 150000.00 - 155000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Human Rights Civil Liberties, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0d9d2c5fecad4b7f9eb021ec484c045b-director-of-finance-the-century-foundation-new-york</t>
+  </si>
+  <si>
     <t>Director of Finance and Assets</t>
   </si>
   <si>
@@ -679,15 +1180,60 @@
     <t>https://www.idealist.org/en/nonprofit-job/ab76a1b181324677b6d898e9ba98e74b-director-of-finance-and-assets-st-philip-neri-catholic-church-fort-mill</t>
   </si>
   <si>
+    <t>Director of Fund Development</t>
+  </si>
+  <si>
+    <t>FundEd Strategies</t>
+  </si>
+  <si>
+    <t>Plainfield, New Jersey</t>
+  </si>
+  <si>
+    <t>USD 100000.00 - 135000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/0eccb594737740ad8f3a8f8c2f4de1a3-director-of-fund-development-funded-strategies-plainfield</t>
+  </si>
+  <si>
+    <t>Director of Growth (Development, Marketing &amp; Communications)</t>
+  </si>
+  <si>
+    <t>Giving Green Research Group</t>
+  </si>
+  <si>
+    <t>USD 135000.00 - 185000.00/year</t>
+  </si>
+  <si>
+    <t>Climate Change, Environment, Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7224c5bf79714303a53d8ed376687c7e-director-of-growth-development-marketing-communications-giving-green-research-group-san-francisco</t>
+  </si>
+  <si>
+    <t>Director of Programs</t>
+  </si>
+  <si>
+    <t>Cave Canem Foundation, Inc.</t>
+  </si>
+  <si>
+    <t>USD 100000.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Race Ethnicity</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/11004711826940be99c4afae2fa9641e-director-of-programs-cave-canem-foundation-inc-new-york</t>
+  </si>
+  <si>
     <t>Director of Workforce Pell Implementation Initiatives</t>
   </si>
   <si>
     <t>LaGuardia Community College</t>
   </si>
   <si>
-    <t>New York, New York</t>
-  </si>
-  <si>
     <t>USD 100000.00 - 125000.00/year</t>
   </si>
   <si>
@@ -697,6 +1243,51 @@
     <t>https://www.idealist.org/en/job/208c0377f556403d95753c418e047f49-director-of-workforce-pell-implementation-initiatives-laguardia-community-college-new-york</t>
   </si>
   <si>
+    <t>Director, Intentional Design for an Equitable Academy (IDEA)</t>
+  </si>
+  <si>
+    <t>American Council of Learned Societies</t>
+  </si>
+  <si>
+    <t>USD 175000.00 - 200000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8f078f693df141e7b8d201de55d8b32f-director-intentional-design-for-an-equitable-academy-idea-american-council-of-learned-societies-new-york</t>
+  </si>
+  <si>
+    <t>Director, People and Culture</t>
+  </si>
+  <si>
+    <t>Tree House Humane Society</t>
+  </si>
+  <si>
+    <t>USD 98242.00 - 115434.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/50306cfeec584090a83c56192973e13e-director-people-and-culture-tree-house-humane-society-chicago</t>
+  </si>
+  <si>
+    <t>Donor Relations Associate</t>
+  </si>
+  <si>
+    <t>Joe and Jill Biden Presidential Library Foundation</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/416d99c82fb5482d90108e339ac8cc85-donor-relations-associate-joe-and-jill-biden-presidential-library-foundation-washington</t>
+  </si>
+  <si>
+    <t>Early Childhood Teacher</t>
+  </si>
+  <si>
+    <t>South-East Asia Center</t>
+  </si>
+  <si>
+    <t>USD 23.00 - 28.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/577539a6429046038b748c031cfb542f-early-childhood-teacher-south-east-asia-center-chicago</t>
+  </si>
+  <si>
     <t>Education Program Coordinator, Convention</t>
   </si>
   <si>
@@ -712,6 +1303,54 @@
     <t>https://www.idealist.org/en/nonprofit-job/86573739146844339ab159e71fd291a1-education-program-coordinator-convention-american-association-for-justice-washington</t>
   </si>
   <si>
+    <t>Educator [South King County]</t>
+  </si>
+  <si>
+    <t>Geeking Out Kids of Color (GOKiC)</t>
+  </si>
+  <si>
+    <t>White Center, Washington</t>
+  </si>
+  <si>
+    <t>USD 26.00 - 29.25/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f345cebfcf084bc4a842186dd330a382-educator-south-king-county-geeking-out-kids-of-color-gokic-white-center</t>
+  </si>
+  <si>
+    <t>Encargado de operaciones</t>
+  </si>
+  <si>
+    <t>Peru Volunteer and Travel</t>
+  </si>
+  <si>
+    <t>Puerto Maldonado, Madre de Dios, PE</t>
+  </si>
+  <si>
+    <t>PEN 1600.00/month</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b0c7d93e5f834d66b71604045b2147ec-encargado-de-operaciones-peru-volunteer-and-travel-puerto-maldonado</t>
+  </si>
+  <si>
+    <t>Events Manager</t>
+  </si>
+  <si>
+    <t>The 5th Avenue Theatre</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ba3645f69cd7463ea8d0fa211ce5575e-events-manager-the-5th-avenue-theatre-seattle</t>
+  </si>
+  <si>
     <t>Executive Assistant</t>
   </si>
   <si>
@@ -727,6 +1366,267 @@
     <t>https://www.idealist.org/en/nonprofit-job/1c6063f79ea8409d92a8cb6764c2ca97-executive-assistant-human-rights-watch-new-york</t>
   </si>
   <si>
+    <t>Executive Director</t>
+  </si>
+  <si>
+    <t>Squash on Track</t>
+  </si>
+  <si>
+    <t>Redwood City, California</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e81669f250fd4956b122313a5a1d96e0-executive-director-squash-on-track-redwood-city</t>
+  </si>
+  <si>
+    <t>Executive Director - Intercommunity Peace &amp; Justice Center</t>
+  </si>
+  <si>
+    <t>Intercommunity Peace &amp; Justice Center</t>
+  </si>
+  <si>
+    <t>USD 90000.00/year</t>
+  </si>
+  <si>
+    <t>Religion Spirituality, Women, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6095a639ee0d4bbda9968007f3fad5d9-executive-director-intercommunity-peace-justice-center-intercommunity-peace-justice-center-seattle</t>
+  </si>
+  <si>
+    <t>Executive Director KC</t>
+  </si>
+  <si>
+    <t>Inner-City Computer Stars Foundation (i.c.stars)</t>
+  </si>
+  <si>
+    <t>Kansas City, Missouri</t>
+  </si>
+  <si>
+    <t>USD 137000.00 - 137000.00/year</t>
+  </si>
+  <si>
+    <t>Economic Development, Education, Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/72ef4fa3e3074f1e9ac2d6618a8a902c-executive-director-kc-inner-city-computer-stars-foundation-icstars-kansas-city</t>
+  </si>
+  <si>
+    <t>Facilitador/a Educativo/a en Yucatán - Nivel Primaria ( Presencial)</t>
+  </si>
+  <si>
+    <t>Educación para Compartir - México</t>
+  </si>
+  <si>
+    <t>Mérida, Yucatán, MX</t>
+  </si>
+  <si>
+    <t>MXN 11430.00 - 11430.00/month</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9b8e755b25874532845a2142fc04ae88-facilitadora-educativoa-en-yucatan-nivel-primaria-presencial-educacion-para-compartir-mexico-merida</t>
+  </si>
+  <si>
+    <t>Family Law Fellow</t>
+  </si>
+  <si>
+    <t>GLBTQ Legal Advocates &amp; Defenders (GLAD Law)</t>
+  </si>
+  <si>
+    <t>Boston, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 82500.00 - 110000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ac2585d6d5b94ef9877d612ace45c88a-family-law-fellow-glbtq-legal-advocates-defenders-glad-law-boston</t>
+  </si>
+  <si>
+    <t>Fund Director, REBUILD.US</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8dbbe9330cb44730bc7928a5f7e8df53-fund-director-rebuildus-assets-under-movement-washington-dc</t>
+  </si>
+  <si>
+    <t>Grant Writer</t>
+  </si>
+  <si>
+    <t>Elba Hope Foundation</t>
+  </si>
+  <si>
+    <t>Agriculture, Children Youth, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/add403742b414c91abc1d69817735a8f-grant-writer-elba-hope-foundation-new-york</t>
+  </si>
+  <si>
+    <t>Samaritan House San Mateo</t>
+  </si>
+  <si>
+    <t>San Mateo, California</t>
+  </si>
+  <si>
+    <t>USD 43.75 - 43.75/hour</t>
+  </si>
+  <si>
+    <t>Economic Development, Health Medicine, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a1c20261728d435f98b581e3737272ca-grant-writer-samaritan-house-san-mateo-san-mateo</t>
+  </si>
+  <si>
+    <t>Grants Officer – Cultural Heritage Preservation</t>
+  </si>
+  <si>
+    <t>USD 120000.00 - 150000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Education, Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/fe8b352848ef47cbb7993b1a2e6d5b70-grants-officer-cultural-heritage-preservation-new-york</t>
+  </si>
+  <si>
+    <t>Grants Officer – Jewish Camping</t>
+  </si>
+  <si>
+    <t>Education, Philanthropy, Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1aa4858f11964b89a74e552da71652e5-grants-officer-jewish-camping-new-york</t>
+  </si>
+  <si>
+    <t>Grants Officer – Jewish Day Schools</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e955668dfbb949458afba98713838124-grants-officer-jewish-day-schools-new-york</t>
+  </si>
+  <si>
+    <t>Grants Officer – Jewish Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/114ce482eb0947b0945a2b622f8fef3e-grants-officer-jewish-education-new-york</t>
+  </si>
+  <si>
+    <t>Grants Officer – Safety Net</t>
+  </si>
+  <si>
+    <t>Disability, Philanthropy, Seniors Retirement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1ed4a112387e42248c48aba0d52aa9a8-grants-officer-safety-net-new-york</t>
+  </si>
+  <si>
+    <t>Head of School (Director)</t>
+  </si>
+  <si>
+    <t>Springforth Community School &amp; Academy</t>
+  </si>
+  <si>
+    <t>Accra, Greater Accra Region, GH</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Religion Spirituality</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d2c6978802994856944686c3990b3558-head-of-school-director-springforth-community-school-academy-accra</t>
+  </si>
+  <si>
+    <t>Housing Case Manager</t>
+  </si>
+  <si>
+    <t>Jenesse Center</t>
+  </si>
+  <si>
+    <t>Los Angeles, California</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Crime Safety, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e5248e8f9a9b4d3187328130cc9a0582-housing-case-manager-jenesse-center-los-angeles</t>
+  </si>
+  <si>
+    <t>Institutional Giving Manager</t>
+  </si>
+  <si>
+    <t>Alley Theatre</t>
+  </si>
+  <si>
+    <t>Houston, Texas</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ca3a33bc742b454390bc605e57f1fcea-institutional-giving-manager-alley-theatre-houston</t>
+  </si>
+  <si>
+    <t>Institutional Giving Officer</t>
+  </si>
+  <si>
+    <t>Union Arts Center</t>
+  </si>
+  <si>
+    <t>USD 80340.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/15b689cf49e848899f00184d42b08c5b-institutional-giving-officer-union-arts-center-seattle</t>
+  </si>
+  <si>
+    <t>Instructional Improvement Specialist</t>
+  </si>
+  <si>
+    <t>Eskolta School Research and Design</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0729abf28279410b874ff2d23fc894c3-instructional-improvement-specialist-eskolta-school-research-and-design-new-york</t>
+  </si>
+  <si>
+    <t>Interim Housing Case Manager</t>
+  </si>
+  <si>
+    <t>Sarah's Circle (Chicago)</t>
+  </si>
+  <si>
+    <t>USD 25.60 - 28.70/hour</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Lgbtq, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/23f98cb2cde3406493e0bfb6c9bd7512-interim-housing-case-manager-sarahs-circle-chicago-chicago</t>
+  </si>
+  <si>
+    <t>LCSW Program Manager</t>
+  </si>
+  <si>
+    <t>A New Way of Life</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 95000.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Substance Abuse Addiction, Women</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ada2b9edfb344550a5c1f66a86315754-lcsw-program-manager-a-new-way-of-life-los-angeles</t>
+  </si>
+  <si>
+    <t>Lead Generator</t>
+  </si>
+  <si>
+    <t>Brigstowe</t>
+  </si>
+  <si>
+    <t>Bristol, England, GB</t>
+  </si>
+  <si>
+    <t>GBP 30559.00 - 32654.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/567c754a281741189ae62c2f9dcb379a-lead-generator-brigstowe-bristol</t>
+  </si>
+  <si>
     <t>Líder de Equipo de Captadores/as de Fondos - Zona Santa Fe (capital)</t>
   </si>
   <si>
@@ -736,6 +1636,57 @@
     <t>https://www.idealist.org/en/nonprofit-job/b1b8f6c7221a4b88a70e0b4d2e7863e4-lider-de-equipo-de-captadoresas-de-fondos-zona-santa-fe-capital-aldeas-infantiles-sos-argentina-santa-fe-de-la-vera-cruz</t>
   </si>
   <si>
+    <t>Major Gifts Associate</t>
+  </si>
+  <si>
+    <t>The WNET Group</t>
+  </si>
+  <si>
+    <t>USD 53000.00 - 57000.00/year</t>
+  </si>
+  <si>
+    <t>Media</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/05114024b11c4fe1b79784c7ddbfdda7-major-gifts-associate-the-wnet-group-new-york</t>
+  </si>
+  <si>
+    <t>Major Gifts Officer</t>
+  </si>
+  <si>
+    <t>Village Health Works</t>
+  </si>
+  <si>
+    <t>Community Development, Economic Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/805ead6582824deb9958a8807cd50830-major-gifts-officer-village-health-works-new-york</t>
+  </si>
+  <si>
+    <t>Major Gifts Officer, National Fundraising &amp; Capital Campaign</t>
+  </si>
+  <si>
+    <t>Meridian International Center</t>
+  </si>
+  <si>
+    <t>USD 160000.00 - 180000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/418f9c2aa0e7494aa2ff081d74d05e60-major-gifts-officer-national-fundraising-capital-campaign-meridian-international-center-washington</t>
+  </si>
+  <si>
+    <t>Manager of Development</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Family, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0830337fcdf547158d0786fdeee07ad0-manager-of-development-jenesse-center-los-angeles</t>
+  </si>
+  <si>
     <t>Manager of Major Gifts and Planned Giving</t>
   </si>
   <si>
@@ -748,6 +1699,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/29819255af3b4234ac5c93be7f76d945-manager-of-major-gifts-and-planned-giving-the-washington-ballet-washington</t>
   </si>
   <si>
+    <t>Manager, Brand Communications</t>
+  </si>
+  <si>
+    <t>Make-A-Wish Metro NY and Western NY</t>
+  </si>
+  <si>
+    <t>Buffalo, New York</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 60000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Health Medicine, Volunteering</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/55d87fb4ce7443fdb98186b8d71f1d8b-manager-brand-communications-make-a-wish-metro-ny-and-western-ny-buffalo</t>
+  </si>
+  <si>
     <t>Manager, Network Operations</t>
   </si>
   <si>
@@ -766,6 +1735,258 @@
     <t>https://www.idealist.org/en/nonprofit-job/eb6baf0e16d3466eb5006841a0766cb7-manager-network-operations-seriousfun-childrens-network-norwalk</t>
   </si>
   <si>
+    <t>Managing Attorney, Legal Services &amp; Family Reunification</t>
+  </si>
+  <si>
+    <t>USD 135000.00 - 140000.00/year</t>
+  </si>
+  <si>
+    <t>Prison Reform, Women, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/bf8672b5ad4f4d2781eda3c4b46c5a5c-managing-attorney-legal-services-family-reunification-a-new-way-of-life-los-angeles</t>
+  </si>
+  <si>
+    <t>Marketing &amp; Communications Manager</t>
+  </si>
+  <si>
+    <t>Treehouse</t>
+  </si>
+  <si>
+    <t>USD 63993.90 - 71672.55/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/72513fd9929b41df8db715665508d585-marketing-communications-manager-treehouse-seattle</t>
+  </si>
+  <si>
+    <t>Marketing Associate</t>
+  </si>
+  <si>
+    <t>Rebuilding Together</t>
+  </si>
+  <si>
+    <t>USD 55250.00 - 58000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Housing Homelessness, Disaster Relief</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/80e1e4d4507f4cc09fb5afbae25aeddd-marketing-associate-rebuilding-together-washington</t>
+  </si>
+  <si>
+    <t>Mental Wellness Therapist</t>
+  </si>
+  <si>
+    <t>Nourishing Hope</t>
+  </si>
+  <si>
+    <t>USD 48000.00 - 54000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Hunger Food Security</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f731f32ac03e41c996d8680974cb3c7a-mental-wellness-therapist-nourishing-hope-chicago</t>
+  </si>
+  <si>
+    <t>Mid-Level Giving Officer</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a24354577958407fa76861965489fb71-mid-level-giving-officer-the-5th-avenue-theatre-seattle</t>
+  </si>
+  <si>
+    <t>Ministry and Program Coordinator</t>
+  </si>
+  <si>
+    <t>The Paulist Center</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7bcdcb51f50245fbab2d7bf6acee5b5b-ministry-and-program-coordinator-the-paulist-center-boston</t>
+  </si>
+  <si>
+    <t>MYPAC Therapist</t>
+  </si>
+  <si>
+    <t>Youth Villages</t>
+  </si>
+  <si>
+    <t>Biloxi, Mississippi</t>
+  </si>
+  <si>
+    <t>USD 52000.00 - 55000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Family, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9efe1bc3149244d4accf1dd9898943f8-mypac-therapist-youth-villages-biloxi</t>
+  </si>
+  <si>
+    <t>Narrative Storyteller</t>
+  </si>
+  <si>
+    <t>Promise of Justice Initiative</t>
+  </si>
+  <si>
+    <t>New Orleans, Louisiana</t>
+  </si>
+  <si>
+    <t>Crime Safety, Human Rights Civil Liberties, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d47fdfa1d1bb4115b514937132f92c70-narrative-storyteller-promise-of-justice-initiative-new-orleans</t>
+  </si>
+  <si>
+    <t>Network Manager- West Coast- Remote- Urgently Hiring!</t>
+  </si>
+  <si>
+    <t>Equal Justice Works</t>
+  </si>
+  <si>
+    <t>Remote (San Francisco, California)</t>
+  </si>
+  <si>
+    <t>USD 84900.00 - 95550.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Legal Assistance, Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/372429c7117a470eb4353e6fdfb25e5c-network-manager-west-coast-remote-urgently-hiring-equal-justice-works-san-francisco</t>
+  </si>
+  <si>
+    <t>New York Theatre Workshop - Executive Assistant</t>
+  </si>
+  <si>
+    <t>New York Theatre Workshop</t>
+  </si>
+  <si>
+    <t>USD 50000.00 - 52000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/04c677bc079b4e5c9aef75977ac192a0-new-york-theatre-workshop-executive-assistant-new-york-theatre-workshop-new-york</t>
+  </si>
+  <si>
+    <t>OneAmerica Votes Canvasser</t>
+  </si>
+  <si>
+    <t>OneAmerica</t>
+  </si>
+  <si>
+    <t>Yakima, Washington</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Human Rights Civil Liberties, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/96477710ec8a4e409b9c85953d816f84-oneamerica-votes-canvasser-oneamerica-yakima</t>
+  </si>
+  <si>
+    <t>Operations and Administrative Support Coordinator</t>
+  </si>
+  <si>
+    <t>Welcoming Home</t>
+  </si>
+  <si>
+    <t>San Rafael, California</t>
+  </si>
+  <si>
+    <t>USD 37.50 - 45.00/hour</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Volunteering, Victim Support</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8fa7adf1beb549558d37ba5511d14ba2-operations-and-administrative-support-coordinator-welcoming-home-san-rafael</t>
+  </si>
+  <si>
+    <t>Operations Assistant</t>
+  </si>
+  <si>
+    <t>USD 22.00 - 24.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/12ea67220e144e679ceb9f9ac6e4af04-operations-assistant-saada-philadelphia</t>
+  </si>
+  <si>
+    <t>Operations Associate</t>
+  </si>
+  <si>
+    <t>Careers In Nonprofits, Inc.</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/60667abadf2f4d34896f670a93620fe7-operations-associate-careers-in-nonprofits-inc-san-francisco</t>
+  </si>
+  <si>
+    <t>Operations Director / Manager</t>
+  </si>
+  <si>
+    <t>Irreplaceable</t>
+  </si>
+  <si>
+    <t>USD 130000.00 - 170000.00/year</t>
+  </si>
+  <si>
+    <t>Policy, Science Technology, Transparency Oversight</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0b1e4b64f5974488997cf279878504fd-operations-director-manager-irreplaceable-new-york</t>
+  </si>
+  <si>
+    <t>Operations Manager</t>
+  </si>
+  <si>
+    <t>Cityseed</t>
+  </si>
+  <si>
+    <t>USD 55000.00/year</t>
+  </si>
+  <si>
+    <t>Agriculture, Entrepreneurship, Hunger Food Security</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e10d73c3efbd4c3bbe33e40f81208e49-operations-manager-cityseed-new-haven</t>
+  </si>
+  <si>
+    <t>Organizer</t>
+  </si>
+  <si>
+    <t>MLK Labor</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Climate Change, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1bcec03d393147b3abf583de903b059e-organizer-mlk-labor-seattle</t>
+  </si>
+  <si>
+    <t>Organizing Director</t>
+  </si>
+  <si>
+    <t>USD 150000.00 - 175000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4a404ad726ed419694db826c59473afa-organizing-director-irreplaceable-new-york</t>
+  </si>
+  <si>
+    <t>Paralegal</t>
+  </si>
+  <si>
+    <t>Federal Public Defender - Western District of Washington</t>
+  </si>
+  <si>
+    <t>USD 83935.00 - 141367.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/government-job/b736b056a92041a89ae29339dd1fbfcd-paralegal-federal-public-defender-western-district-of-washington-seattle</t>
+  </si>
+  <si>
     <t>Part-Time Administrative Assistant</t>
   </si>
   <si>
@@ -781,36 +2002,153 @@
     <t>https://www.idealist.org/en/nonprofit-job/689a29b2b73940469abef61c396c1a1a-part-time-administrative-assistant-alpha-phi-alpha-older-adult-center-queens-county</t>
   </si>
   <si>
+    <t>Part-time Donor Data &amp; Development Assistant</t>
+  </si>
+  <si>
+    <t>Girl Scouts of Connecticut Inc</t>
+  </si>
+  <si>
+    <t>North Haven, CT</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/98167cc49eb3464ea1e6cbdd7cf5a363-part-time-donor-data-development-assistant-girl-scouts-of-connecticut-inc-north-haven</t>
+  </si>
+  <si>
+    <t>Part-Time Office Administrator</t>
+  </si>
+  <si>
+    <t>La Raza Centro Legal, Inc</t>
+  </si>
+  <si>
+    <t>USD 36.39 - 37.55/hour</t>
+  </si>
+  <si>
+    <t>Legal Assistance, Immigrants Or Refugees, Lgbtq</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8c6967a0baa54de4bb1669d576b5793b-part-time-office-administrator-la-raza-centro-legal-inc-san-francisco</t>
+  </si>
+  <si>
+    <t>Partnership &amp; Advertising Sales Contractor</t>
+  </si>
+  <si>
+    <t>Sierra Club</t>
+  </si>
+  <si>
+    <t>USD 2000.00 - 15000.00/month</t>
+  </si>
+  <si>
+    <t>Environment, Children Youth, Climate Change</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/abb22326f9ba47b88743ff3cd91b4880-partnership-advertising-sales-contractor-sierra-club-oakland</t>
+  </si>
+  <si>
+    <t>Payroll Administrator</t>
+  </si>
+  <si>
+    <t>USD 43.26 - 43.26/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/cf850979ab394d95a96b8c2e5e18b5ff-payroll-administrator-samaritan-house-san-mateo-san-mateo</t>
+  </si>
+  <si>
     <t>People &amp; Culture Manager</t>
   </si>
   <si>
     <t>Chicago Votes</t>
   </si>
   <si>
-    <t>Chicago, Illinois</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/74ef62deced54e0bbb0ad255c70d6aae-people-culture-manager-chicago-votes-chicago</t>
   </si>
   <si>
+    <t>PRESIDENT &amp; CHIEF EXECUTIVE OFFICER</t>
+  </si>
+  <si>
+    <t>South Sound YMCA</t>
+  </si>
+  <si>
+    <t>Olympia, WA</t>
+  </si>
+  <si>
+    <t>USD 210000.00 - 225000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8a941690eaae431a8b70c126626d8976-president-chief-executive-officer-south-sound-ymca-olympia</t>
+  </si>
+  <si>
     <t>Profesional para tareas administrativas</t>
   </si>
   <si>
-    <t>Contract</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/836d574c03134a29880fbdcb15c4f8d7-profesional-para-tareas-administrativas-aldeas-infantiles-sos-argentina-buenos-aires</t>
   </si>
   <si>
+    <t>Program Coordinator - Ossining, NY</t>
+  </si>
+  <si>
+    <t>Girls Inc. of Westchester County</t>
+  </si>
+  <si>
+    <t>Ossining, New York</t>
+  </si>
+  <si>
+    <t>USD 30000.00 - 30000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Women</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3b0762a9ca354b78a79e1d0b017d4636-program-coordinator-ossining-ny-girls-inc-of-westchester-county-ossining</t>
+  </si>
+  <si>
+    <t>Program Coordinator, Coachella Valley</t>
+  </si>
+  <si>
+    <t>Armed Services Arts Partnership (ASAP)</t>
+  </si>
+  <si>
+    <t>Remote (Coachella, California)</t>
+  </si>
+  <si>
+    <t>USD 45000.00 - 55000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Veterans</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8e5ec60b28f34f9cb7ed76369c659640-program-coordinator-coachella-valley-armed-services-arts-partnership-asap-coachella</t>
+  </si>
+  <si>
+    <t>Program Data Coordinator</t>
+  </si>
+  <si>
+    <t>Compass Pro Bono</t>
+  </si>
+  <si>
+    <t>USD 45000.00 - 45000.00/year</t>
+  </si>
+  <si>
+    <t>Volunteering</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ec66184a8ba3496e8f4c2cce315b3976-program-data-coordinator-compass-pro-bono-washington</t>
+  </si>
+  <si>
+    <t>Program Manager, Los Angeles &amp; Coachella Valley</t>
+  </si>
+  <si>
+    <t>Remote (Los Angeles, California)</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/cf597d3bc89d4d19a7873e970f6c5aa9-program-manager-los-angeles-coachella-valley-armed-services-arts-partnership-asap-los-angeles</t>
+  </si>
+  <si>
     <t>Program Specialist, Boston - 30hrs/week - Hybrid</t>
   </si>
   <si>
     <t>Literations</t>
   </si>
   <si>
-    <t>Boston, Massachusetts</t>
-  </si>
-  <si>
     <t>USD 54000.00 - 59000.00/year</t>
   </si>
   <si>
@@ -820,6 +2158,264 @@
     <t>https://www.idealist.org/en/nonprofit-job/acdb85e42be64ee4a8af64e2a7cb5776-program-specialist-boston-30hrsweek-hybrid-literations-boston</t>
   </si>
   <si>
+    <t>Programs Coordinator</t>
+  </si>
+  <si>
+    <t>Our Family Coalition</t>
+  </si>
+  <si>
+    <t>USD 22.39 - 25.64/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Lgbtq, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8e2b1645b3f34e0ba2e83a0b9cb1dd90-programs-coordinator-our-family-coalition-san-francisco</t>
+  </si>
+  <si>
+    <t>RADCo Coordinator</t>
+  </si>
+  <si>
+    <t>Eviction Defense Collaborative</t>
+  </si>
+  <si>
+    <t>USD 32.42 - 37.47/hour</t>
+  </si>
+  <si>
+    <t>Conflict Resolution, Housing Homelessness, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/452482dcd68e4ccea4865442e657c90d-radco-coordinator-eviction-defense-collaborative-san-francisco</t>
+  </si>
+  <si>
+    <t>Research &amp; Data Assistant</t>
+  </si>
+  <si>
+    <t>The Commonwealth Institute for Fiscal Analysis</t>
+  </si>
+  <si>
+    <t>Richmond, Virginia</t>
+  </si>
+  <si>
+    <t>Policy, Research Social Science</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/17ca3520d4aa4df0a2a7d6b301fe6b73-research-data-assistant-the-commonwealth-institute-for-fiscal-analysis-richmond</t>
+  </si>
+  <si>
+    <t>Research Assistant (Job ID: 2026-3891)</t>
+  </si>
+  <si>
+    <t>1. Resident Employee (Hybrid)</t>
+  </si>
+  <si>
+    <t>USD 50300.00 - 75400.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/6d1d4a9c72cd42d689172a5bed6a3035-research-assistant-job-id-2026-3891-1-resident-employee-hybrid-washington</t>
+  </si>
+  <si>
+    <t>Research Assistant, The Hamilton Project (Job ID: 2026-3893)</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/439ed872b4444917b3a9d14e1c430a60-research-assistant-the-hamilton-project-job-id-2026-3893-1-resident-employee-hybrid-washington</t>
+  </si>
+  <si>
+    <t>School Bus Driver</t>
+  </si>
+  <si>
+    <t>Marin Horizon School</t>
+  </si>
+  <si>
+    <t>Mill Valley, California</t>
+  </si>
+  <si>
+    <t>USD 30.00 - 40.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/aec2d9a3e0bc48ba9fb8e186d1e87399-school-bus-driver-marin-horizon-school-mill-valley</t>
+  </si>
+  <si>
+    <t>Senior Accountant</t>
+  </si>
+  <si>
+    <t>Roseland, New Jersey</t>
+  </si>
+  <si>
+    <t>USD 86900.00 - 95800.00/year</t>
+  </si>
+  <si>
+    <t>Volunteering, Children Youth, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/bdf0e83fa7d249cf91f90091278be48f-senior-accountant-roseland</t>
+  </si>
+  <si>
+    <t>Senior Consultant (Grant Writer, Foundation Relations, Institutional Giving)</t>
+  </si>
+  <si>
+    <t>CIMA Consulting</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/322e4ae1de324c2583e3a9545dd1729b-senior-consultant-grant-writer-foundation-relations-institutional-giving-cima-consulting-charlottesville</t>
+  </si>
+  <si>
+    <t>Senior Digital Manager</t>
+  </si>
+  <si>
+    <t>USD 120000.00 - 145000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/28b77aeed83b48e2ad2080ad19979cac-senior-digital-manager-irreplaceable-new-york</t>
+  </si>
+  <si>
+    <t>Senior Digital Strategy &amp; Engagement Associate (part-time)</t>
+  </si>
+  <si>
+    <t>USD 38500.00 - 40000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/aa94715132b842b6a3cd33090f84f019-senior-digital-strategy-engagement-associate-part-time-national-center-for-youth-law-ncyl-oakland</t>
+  </si>
+  <si>
+    <t>Senior Director for Development, Communications and Marketing</t>
+  </si>
+  <si>
+    <t>Institute for Islamic, Christian, and Jewish Studies</t>
+  </si>
+  <si>
+    <t>Baltimore, Maryland</t>
+  </si>
+  <si>
+    <t>USD 115000.00 - 125000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Education, Religion Spirituality</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3562e73fdadf4d0ca831f3f2396d9573-senior-director-for-development-communications-and-marketing-institute-for-islamic-christian-and-jewish-studies-baltimore</t>
+  </si>
+  <si>
+    <t>Senior Director of Supportive Services</t>
+  </si>
+  <si>
+    <t>SHARE Cancer Support</t>
+  </si>
+  <si>
+    <t>Health Medicine, Lgbtq, Women</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/60868e46aadd4d8391ad99d1011b0031-senior-director-of-supportive-services-share-cancer-support-new-york</t>
+  </si>
+  <si>
+    <t>Senior Director, Legal Counsel (Fixed Term)</t>
+  </si>
+  <si>
+    <t>United Way of New York City</t>
+  </si>
+  <si>
+    <t>USD 115193.00 - 120000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f839b407455141d890f7c850897bbdce-senior-director-legal-counsel-fixed-term-united-way-of-new-york-city-new-york</t>
+  </si>
+  <si>
+    <t>Senior Fundraising Consultant – Campaign &amp; Donor Development</t>
+  </si>
+  <si>
+    <t>Psychological and Developmental Relief Society</t>
+  </si>
+  <si>
+    <t>USD 2000.00 - 4000.00/month</t>
+  </si>
+  <si>
+    <t>Children Youth, Economic Development, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6ef277fbf18c43f3b02ced973e3f2efa-senior-fundraising-consultant-campaign-donor-development-psychological-and-developmental-relief-society-gaza</t>
+  </si>
+  <si>
+    <t>Senior Health Care Policy Analyst</t>
+  </si>
+  <si>
+    <t>USD 73000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/35282756331842148711d85d585f9cbe-senior-health-care-policy-analyst-the-commonwealth-institute-for-fiscal-analysis-richmond</t>
+  </si>
+  <si>
+    <t>Senior Manager, Human Resources</t>
+  </si>
+  <si>
+    <t>Brooklyn Defender Services</t>
+  </si>
+  <si>
+    <t>Brooklyn, NY</t>
+  </si>
+  <si>
+    <t>USD 140000.00 - 150000.00/year</t>
+  </si>
+  <si>
+    <t>Family, Immigrants Or Refugees, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4dd808aafca64788bac77454df9acac7-senior-manager-human-resources-brooklyn-defender-services-brooklyn</t>
+  </si>
+  <si>
+    <t>Senior Research Assistant, The Hamilton Project (Job ID: 2026-3892)</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/e942d924b2854901943ad7e6a64adca4-senior-research-assistant-the-hamilton-project-job-id-2026-3892-1-resident-employee-hybrid-washington</t>
+  </si>
+  <si>
+    <t>Senior Research, Mixed Methods</t>
+  </si>
+  <si>
+    <t>USD 100000.00 - 120000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5a879c46239148019d8180e1d0360c48-senior-research-mixed-methods-goodpower-boston</t>
+  </si>
+  <si>
+    <t>Senior Staff Attorney</t>
+  </si>
+  <si>
+    <t>Immigrant Legal Resource Center</t>
+  </si>
+  <si>
+    <t>USD 112492.23/year</t>
+  </si>
+  <si>
+    <t>Immigrants Or Refugees, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a07900084722423cadf17a83a69b968c-senior-staff-attorney-immigrant-legal-resource-center-san-francisco</t>
+  </si>
+  <si>
+    <t>Shelter Services - Bilingual Case Manager</t>
+  </si>
+  <si>
+    <t>South San Francisco, California</t>
+  </si>
+  <si>
+    <t>USD 31.50 - 31.50/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/68b1f61d66654256bae2f9e686561284-shelter-services-bilingual-case-manager-samaritan-house-san-mateo-south-san-francisco</t>
+  </si>
+  <si>
+    <t>Social Work Assistant</t>
+  </si>
+  <si>
+    <t>Alliance for Children's Rights</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2924f1e185644f19b4130ae2a6d41eb8-social-work-assistant-alliance-for-childrens-rights-los-angeles</t>
+  </si>
+  <si>
     <t>Social Worker</t>
   </si>
   <si>
@@ -838,6 +2434,63 @@
     <t>https://www.idealist.org/en/consultant-job/b3d7fdec26fc45e2b1ff32540886fb60-social-worker-pracademic-partners-bath</t>
   </si>
   <si>
+    <t>Columbia Law School</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/543faaae0be94b838c606995af473986-social-worker-columbia-law-school-new-york</t>
+  </si>
+  <si>
+    <t>Specialist, Data Entry</t>
+  </si>
+  <si>
+    <t>National Association of Community Health Centers</t>
+  </si>
+  <si>
+    <t>Bethesda, MD</t>
+  </si>
+  <si>
+    <t>USD 63000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/195925cd74b84408be802260df3c6bdd-specialist-data-entry-national-association-of-community-health-centers-bethesda</t>
+  </si>
+  <si>
+    <t>Staff Accountant - St. Ambrose Housing Aid Center</t>
+  </si>
+  <si>
+    <t>NeighborWorks Affiliates</t>
+  </si>
+  <si>
+    <t>USD 60000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Economic Development, Financial Literacy Personal Finance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ccd224c27dac4f0a942c795e94db578f-staff-accountant-st-ambrose-housing-aid-center-neighborworks-affiliates-baltimore</t>
+  </si>
+  <si>
+    <t>Staff Attorney</t>
+  </si>
+  <si>
+    <t>Disability Rights New York</t>
+  </si>
+  <si>
+    <t>Albany, New York</t>
+  </si>
+  <si>
+    <t>USD 62000.00 - 115000.00/year</t>
+  </si>
+  <si>
+    <t>Disability, Human Rights Civil Liberties, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/abe9f69ad7f544e1bae909587714fa90-staff-attorney-disability-rights-new-york-albany</t>
+  </si>
+  <si>
     <t>Staff Attorney - Family Law Unit</t>
   </si>
   <si>
@@ -853,21 +2506,114 @@
     <t>https://www.idealist.org/en/nonprofit-job/22089149714942c2ab4b895b2cc4a832-staff-attorney-family-law-unit-greater-boston-legal-services-boston</t>
   </si>
   <si>
+    <t>Staff Attorney, Tenant Advocacy Program</t>
+  </si>
+  <si>
+    <t>Catholic Migration Services</t>
+  </si>
+  <si>
+    <t>USD 79393.12 - 89846.66/year</t>
+  </si>
+  <si>
+    <t>Community Development, Economic Development, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/18fb31ca6e814632b796241725751bb5-staff-attorney-tenant-advocacy-program-catholic-migration-services-queens-county</t>
+  </si>
+  <si>
+    <t>Success Coach</t>
+  </si>
+  <si>
+    <t>USD 32.50 - 32.50/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c8ad61e7f1664f2492e9ff44e9c48a28-success-coach-samaritan-house-san-mateo-san-mateo</t>
+  </si>
+  <si>
+    <t>Sunday School (in New York City) Quran and Islamic Teacher for Children</t>
+  </si>
+  <si>
+    <t>Cordoba House</t>
+  </si>
+  <si>
+    <t>USD 18.00 - 25.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3e3a7ee0782f4eafbd0ef6e2dce365a8-sunday-school-in-new-york-city-quran-and-islamic-teacher-for-children-cordoba-house-new-york</t>
+  </si>
+  <si>
+    <t>Supervising Social Worker</t>
+  </si>
+  <si>
+    <t>USD 72000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>Women, Family, Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ab9f14a615d546e194fde74cf17af200-supervising-social-worker-a-new-way-of-life-los-angeles</t>
+  </si>
+  <si>
+    <t>Talent Acquisition Manager</t>
+  </si>
+  <si>
+    <t>USD 115000.00 - 130000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3e663102f5664cefbc920ff1114677ad-talent-acquisition-manager-brooklyn-defender-services-brooklyn</t>
+  </si>
+  <si>
+    <t>UX Team Lead</t>
+  </si>
+  <si>
+    <t>The Tor Project</t>
+  </si>
+  <si>
+    <t>USD 110000.00 - 121275.00/year</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Science Technology</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/053d1db464054f22bff1f2033fd0f5ae-ux-team-lead-the-tor-project-winchester</t>
+  </si>
+  <si>
+    <t>Vice President, Technology &amp; Digital Strategy</t>
+  </si>
+  <si>
+    <t>Shatterproof</t>
+  </si>
+  <si>
+    <t>USD 175000.00 - 190000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Education, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/643f31f74fb94cb9b4427060801b77a5-vice-president-technology-digital-strategy-shatterproof-norwalk</t>
+  </si>
+  <si>
     <t>Volunteer Coordinator (Full-time)</t>
   </si>
   <si>
     <t>Cholangiocarcinoma Foundation</t>
   </si>
   <si>
-    <t>Remote</t>
-  </si>
-  <si>
-    <t>Health Medicine</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/e1f0208eb10c46b7945b0d3227223d21-volunteer-coordinator-full-time-cholangiocarcinoma-foundation-herriman</t>
   </si>
   <si>
+    <t>Worker Resource Center Program Manager</t>
+  </si>
+  <si>
+    <t>USD 33.65 - 33.65/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e703283dd8254cc6ac49c4b2cc595136-worker-resource-center-program-manager-samaritan-house-san-mateo-san-mateo</t>
+  </si>
+  <si>
     <t>Workforce Data Specialist</t>
   </si>
   <si>
@@ -881,6 +2627,15 @@
   </si>
   <si>
     <t>https://www.idealist.org/en/job/094ce9fce311412f90ea7e06c3bc42e2-workforce-specialist-financial-aid-liaison-laguardia-community-college-new-york</t>
+  </si>
+  <si>
+    <t>Youth Programs Instructor: Manhattan &amp; Bronx (Part-time)</t>
+  </si>
+  <si>
+    <t>Teens for Food Justice</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d8f14d7deabb424bb30cf00ef47c4ef1-youth-programs-instructor-manhattan-bronx-part-time-teens-for-food-justice-new-york</t>
   </si>
   <si>
     <t>Zona Córdoba (capital) - Líder de Equipo de Captadores/as de Fondos</t>
@@ -1850,7 +3605,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -1889,8 +3644,34 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C2" t="s">
+        <v>136</v>
+      </c>
+      <c r="D2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E2" t="s">
+        <v>138</v>
+      </c>
+      <c r="F2" t="s">
+        <v>139</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>140</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -1898,7 +3679,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H34"/>
+  <dimension ref="A1:H165"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -1939,48 +3720,48 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="B2" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="C2" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="D2" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="E2" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="F2" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="B3" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="C3" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="D3" t="s">
         <v>144</v>
       </c>
       <c r="E3" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="F3" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1988,712 +3769,3725 @@
         <v>148</v>
       </c>
       <c r="B4" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="C4" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="D4" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="E4" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="F4" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="B5" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="C5" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="D5" t="s">
-        <v>137</v>
+        <v>162</v>
       </c>
       <c r="E5" t="s">
-        <v>157</v>
+        <v>138</v>
       </c>
       <c r="F5" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="B6" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="C6" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="D6" t="s">
-        <v>144</v>
+        <v>168</v>
       </c>
       <c r="E6" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="F6" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="B7" t="s">
-        <v>161</v>
+        <v>172</v>
       </c>
       <c r="C7" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="D7" t="s">
         <v>144</v>
       </c>
       <c r="E7" t="s">
-        <v>145</v>
+        <v>174</v>
       </c>
       <c r="F7" t="s">
-        <v>167</v>
+        <v>138</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="B8" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="C8" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="D8" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="E8" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="F8" t="s">
-        <v>173</v>
+        <v>138</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="B9" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="C9" t="s">
-        <v>171</v>
+        <v>183</v>
       </c>
       <c r="D9" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="E9" t="s">
-        <v>172</v>
+        <v>184</v>
       </c>
       <c r="F9" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="B10" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="C10" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="D10" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="E10" t="s">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="F10" t="s">
-        <v>145</v>
+        <v>191</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>182</v>
+        <v>192</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="B11" t="s">
-        <v>184</v>
+        <v>194</v>
       </c>
       <c r="C11" t="s">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="D11" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="E11" t="s">
-        <v>145</v>
+        <v>196</v>
       </c>
       <c r="F11" t="s">
-        <v>145</v>
+        <v>197</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>187</v>
+        <v>199</v>
       </c>
       <c r="B12" t="s">
-        <v>161</v>
+        <v>200</v>
       </c>
       <c r="C12" t="s">
-        <v>162</v>
+        <v>201</v>
       </c>
       <c r="D12" t="s">
-        <v>137</v>
+        <v>202</v>
       </c>
       <c r="E12" t="s">
-        <v>145</v>
+        <v>203</v>
       </c>
       <c r="F12" t="s">
-        <v>188</v>
+        <v>204</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>189</v>
+        <v>205</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>190</v>
+        <v>206</v>
       </c>
       <c r="B13" t="s">
-        <v>161</v>
+        <v>200</v>
       </c>
       <c r="C13" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="D13" t="s">
-        <v>137</v>
+        <v>202</v>
       </c>
       <c r="E13" t="s">
-        <v>145</v>
+        <v>203</v>
       </c>
       <c r="F13" t="s">
-        <v>192</v>
+        <v>204</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="B14" t="s">
-        <v>161</v>
+        <v>209</v>
       </c>
       <c r="C14" t="s">
-        <v>195</v>
+        <v>210</v>
       </c>
       <c r="D14" t="s">
-        <v>137</v>
+        <v>162</v>
       </c>
       <c r="E14" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="F14" t="s">
-        <v>196</v>
+        <v>211</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>197</v>
+        <v>212</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>198</v>
+        <v>213</v>
       </c>
       <c r="B15" t="s">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="C15" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="D15" t="s">
-        <v>137</v>
+        <v>162</v>
       </c>
       <c r="E15" t="s">
-        <v>201</v>
+        <v>138</v>
       </c>
       <c r="F15" t="s">
-        <v>202</v>
+        <v>215</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>203</v>
+        <v>216</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="B16" t="s">
-        <v>205</v>
+        <v>218</v>
       </c>
       <c r="C16" t="s">
-        <v>206</v>
+        <v>219</v>
       </c>
       <c r="D16" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="E16" t="s">
-        <v>207</v>
+        <v>220</v>
       </c>
       <c r="F16" t="s">
-        <v>208</v>
+        <v>221</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>209</v>
+        <v>222</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>210</v>
+        <v>223</v>
       </c>
       <c r="B17" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="C17" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="D17" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="E17" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="F17" t="s">
-        <v>214</v>
+        <v>224</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>215</v>
+        <v>225</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="B18" t="s">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="C18" t="s">
-        <v>218</v>
+        <v>173</v>
       </c>
       <c r="D18" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="E18" t="s">
-        <v>145</v>
+        <v>228</v>
       </c>
       <c r="F18" t="s">
-        <v>219</v>
+        <v>138</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>220</v>
+        <v>229</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="B19" t="s">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="C19" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="D19" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="E19" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F19" t="s">
-        <v>225</v>
+        <v>138</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="B20" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="C20" t="s">
-        <v>212</v>
+        <v>237</v>
       </c>
       <c r="D20" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="E20" t="s">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="F20" t="s">
-        <v>230</v>
+        <v>138</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="B21" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="C21" t="s">
-        <v>223</v>
+        <v>173</v>
       </c>
       <c r="D21" t="s">
-        <v>137</v>
+        <v>162</v>
       </c>
       <c r="E21" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="F21" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="B22" t="s">
-        <v>161</v>
+        <v>246</v>
       </c>
       <c r="C22" t="s">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="D22" t="s">
         <v>144</v>
       </c>
       <c r="E22" t="s">
-        <v>145</v>
+        <v>248</v>
       </c>
       <c r="F22" t="s">
-        <v>167</v>
+        <v>249</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>239</v>
+        <v>250</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>240</v>
+        <v>251</v>
       </c>
       <c r="B23" t="s">
-        <v>241</v>
+        <v>252</v>
       </c>
       <c r="C23" t="s">
-        <v>212</v>
+        <v>247</v>
       </c>
       <c r="D23" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="E23" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="F23" t="s">
-        <v>145</v>
+        <v>254</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="B24" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="C24" t="s">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="D24" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="E24" t="s">
-        <v>247</v>
+        <v>138</v>
       </c>
       <c r="F24" t="s">
-        <v>248</v>
+        <v>138</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="B25" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="C25" t="s">
-        <v>171</v>
+        <v>262</v>
       </c>
       <c r="D25" t="s">
         <v>144</v>
       </c>
       <c r="E25" t="s">
-        <v>252</v>
+        <v>138</v>
       </c>
       <c r="F25" t="s">
-        <v>253</v>
+        <v>138</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="B26" t="s">
-        <v>256</v>
+        <v>142</v>
       </c>
       <c r="C26" t="s">
-        <v>257</v>
+        <v>247</v>
       </c>
       <c r="D26" t="s">
         <v>144</v>
       </c>
       <c r="E26" t="s">
-        <v>145</v>
+        <v>265</v>
       </c>
       <c r="F26" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="B27" t="s">
-        <v>161</v>
+        <v>268</v>
       </c>
       <c r="C27" t="s">
-        <v>166</v>
+        <v>247</v>
       </c>
       <c r="D27" t="s">
-        <v>260</v>
+        <v>144</v>
       </c>
       <c r="E27" t="s">
-        <v>145</v>
+        <v>269</v>
       </c>
       <c r="F27" t="s">
-        <v>192</v>
+        <v>270</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>261</v>
+        <v>271</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>262</v>
+        <v>272</v>
       </c>
       <c r="B28" t="s">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="C28" t="s">
-        <v>264</v>
+        <v>274</v>
       </c>
       <c r="D28" t="s">
         <v>144</v>
       </c>
       <c r="E28" t="s">
-        <v>265</v>
+        <v>138</v>
       </c>
       <c r="F28" t="s">
-        <v>266</v>
+        <v>138</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="B29" t="s">
-        <v>269</v>
+        <v>138</v>
       </c>
       <c r="C29" t="s">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="D29" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="E29" t="s">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="F29" t="s">
-        <v>272</v>
+        <v>138</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="B30" t="s">
-        <v>275</v>
+        <v>209</v>
       </c>
       <c r="C30" t="s">
-        <v>264</v>
+        <v>210</v>
       </c>
       <c r="D30" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="E30" t="s">
-        <v>276</v>
+        <v>138</v>
       </c>
       <c r="F30" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="B31" t="s">
-        <v>280</v>
+        <v>209</v>
       </c>
       <c r="C31" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="D31" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="E31" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="F31" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="B32" t="s">
-        <v>222</v>
+        <v>209</v>
       </c>
       <c r="C32" t="s">
-        <v>223</v>
+        <v>288</v>
       </c>
       <c r="D32" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="E32" t="s">
-        <v>285</v>
+        <v>138</v>
       </c>
       <c r="F32" t="s">
-        <v>225</v>
+        <v>289</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="B33" t="s">
-        <v>222</v>
+        <v>292</v>
       </c>
       <c r="C33" t="s">
-        <v>223</v>
+        <v>293</v>
       </c>
       <c r="D33" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="E33" t="s">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="F33" t="s">
-        <v>225</v>
+        <v>295</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>288</v>
+        <v>296</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="B34" t="s">
-        <v>161</v>
+        <v>298</v>
       </c>
       <c r="C34" t="s">
+        <v>299</v>
+      </c>
+      <c r="D34" t="s">
+        <v>144</v>
+      </c>
+      <c r="E34" t="s">
+        <v>300</v>
+      </c>
+      <c r="F34" t="s">
+        <v>301</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>303</v>
+      </c>
+      <c r="B35" t="s">
+        <v>304</v>
+      </c>
+      <c r="C35" t="s">
+        <v>210</v>
+      </c>
+      <c r="D35" t="s">
+        <v>144</v>
+      </c>
+      <c r="E35" t="s">
+        <v>138</v>
+      </c>
+      <c r="F35" t="s">
+        <v>305</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>307</v>
+      </c>
+      <c r="B36" t="s">
+        <v>308</v>
+      </c>
+      <c r="C36" t="s">
+        <v>299</v>
+      </c>
+      <c r="D36" t="s">
+        <v>144</v>
+      </c>
+      <c r="E36" t="s">
+        <v>309</v>
+      </c>
+      <c r="F36" t="s">
+        <v>310</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>312</v>
+      </c>
+      <c r="B37" t="s">
+        <v>313</v>
+      </c>
+      <c r="C37" t="s">
+        <v>314</v>
+      </c>
+      <c r="D37" t="s">
+        <v>144</v>
+      </c>
+      <c r="E37" t="s">
+        <v>315</v>
+      </c>
+      <c r="F37" t="s">
+        <v>316</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>318</v>
+      </c>
+      <c r="B38" t="s">
+        <v>319</v>
+      </c>
+      <c r="C38" t="s">
+        <v>173</v>
+      </c>
+      <c r="D38" t="s">
+        <v>144</v>
+      </c>
+      <c r="E38" t="s">
+        <v>320</v>
+      </c>
+      <c r="F38" t="s">
+        <v>321</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>323</v>
+      </c>
+      <c r="B39" t="s">
+        <v>324</v>
+      </c>
+      <c r="C39" t="s">
+        <v>325</v>
+      </c>
+      <c r="D39" t="s">
+        <v>144</v>
+      </c>
+      <c r="E39" t="s">
+        <v>326</v>
+      </c>
+      <c r="F39" t="s">
+        <v>327</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>323</v>
+      </c>
+      <c r="B40" t="s">
+        <v>329</v>
+      </c>
+      <c r="C40" t="s">
+        <v>330</v>
+      </c>
+      <c r="D40" t="s">
+        <v>144</v>
+      </c>
+      <c r="E40" t="s">
+        <v>331</v>
+      </c>
+      <c r="F40" t="s">
+        <v>332</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>334</v>
+      </c>
+      <c r="B41" t="s">
+        <v>335</v>
+      </c>
+      <c r="C41" t="s">
+        <v>336</v>
+      </c>
+      <c r="D41" t="s">
+        <v>144</v>
+      </c>
+      <c r="E41" t="s">
+        <v>337</v>
+      </c>
+      <c r="F41" t="s">
+        <v>138</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>339</v>
+      </c>
+      <c r="B42" t="s">
+        <v>194</v>
+      </c>
+      <c r="C42" t="s">
+        <v>195</v>
+      </c>
+      <c r="D42" t="s">
+        <v>144</v>
+      </c>
+      <c r="E42" t="s">
+        <v>340</v>
+      </c>
+      <c r="F42" t="s">
+        <v>197</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>342</v>
+      </c>
+      <c r="B43" t="s">
+        <v>319</v>
+      </c>
+      <c r="C43" t="s">
+        <v>247</v>
+      </c>
+      <c r="D43" t="s">
+        <v>144</v>
+      </c>
+      <c r="E43" t="s">
+        <v>343</v>
+      </c>
+      <c r="F43" t="s">
+        <v>321</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>345</v>
+      </c>
+      <c r="B44" t="s">
+        <v>346</v>
+      </c>
+      <c r="C44" t="s">
+        <v>347</v>
+      </c>
+      <c r="D44" t="s">
+        <v>144</v>
+      </c>
+      <c r="E44" t="s">
+        <v>348</v>
+      </c>
+      <c r="F44" t="s">
+        <v>349</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>351</v>
+      </c>
+      <c r="B45" t="s">
+        <v>352</v>
+      </c>
+      <c r="C45" t="s">
+        <v>353</v>
+      </c>
+      <c r="D45" t="s">
+        <v>168</v>
+      </c>
+      <c r="E45" t="s">
+        <v>354</v>
+      </c>
+      <c r="F45" t="s">
+        <v>355</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>357</v>
+      </c>
+      <c r="B46" t="s">
+        <v>358</v>
+      </c>
+      <c r="C46" t="s">
+        <v>359</v>
+      </c>
+      <c r="D46" t="s">
+        <v>144</v>
+      </c>
+      <c r="E46" t="s">
+        <v>360</v>
+      </c>
+      <c r="F46" t="s">
+        <v>361</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>363</v>
+      </c>
+      <c r="B47" t="s">
+        <v>364</v>
+      </c>
+      <c r="C47" t="s">
+        <v>365</v>
+      </c>
+      <c r="D47" t="s">
+        <v>144</v>
+      </c>
+      <c r="E47" t="s">
+        <v>366</v>
+      </c>
+      <c r="F47" t="s">
+        <v>367</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>369</v>
+      </c>
+      <c r="B48" t="s">
+        <v>142</v>
+      </c>
+      <c r="C48" t="s">
+        <v>247</v>
+      </c>
+      <c r="D48" t="s">
+        <v>370</v>
+      </c>
+      <c r="E48" t="s">
+        <v>371</v>
+      </c>
+      <c r="F48" t="s">
+        <v>146</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>373</v>
+      </c>
+      <c r="B49" t="s">
+        <v>374</v>
+      </c>
+      <c r="C49" t="s">
+        <v>359</v>
+      </c>
+      <c r="D49" t="s">
+        <v>144</v>
+      </c>
+      <c r="E49" t="s">
+        <v>375</v>
+      </c>
+      <c r="F49" t="s">
+        <v>376</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>378</v>
+      </c>
+      <c r="B50" t="s">
+        <v>379</v>
+      </c>
+      <c r="C50" t="s">
+        <v>173</v>
+      </c>
+      <c r="D50" t="s">
+        <v>144</v>
+      </c>
+      <c r="E50" t="s">
+        <v>380</v>
+      </c>
+      <c r="F50" t="s">
+        <v>381</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>383</v>
+      </c>
+      <c r="B51" t="s">
+        <v>384</v>
+      </c>
+      <c r="C51" t="s">
+        <v>385</v>
+      </c>
+      <c r="D51" t="s">
+        <v>144</v>
+      </c>
+      <c r="E51" t="s">
+        <v>138</v>
+      </c>
+      <c r="F51" t="s">
+        <v>386</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>388</v>
+      </c>
+      <c r="B52" t="s">
+        <v>389</v>
+      </c>
+      <c r="C52" t="s">
+        <v>390</v>
+      </c>
+      <c r="D52" t="s">
+        <v>144</v>
+      </c>
+      <c r="E52" t="s">
+        <v>391</v>
+      </c>
+      <c r="F52" t="s">
+        <v>392</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>394</v>
+      </c>
+      <c r="B53" t="s">
+        <v>395</v>
+      </c>
+      <c r="C53" t="s">
+        <v>247</v>
+      </c>
+      <c r="D53" t="s">
+        <v>144</v>
+      </c>
+      <c r="E53" t="s">
+        <v>396</v>
+      </c>
+      <c r="F53" t="s">
+        <v>397</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>399</v>
+      </c>
+      <c r="B54" t="s">
+        <v>400</v>
+      </c>
+      <c r="C54" t="s">
+        <v>173</v>
+      </c>
+      <c r="D54" t="s">
+        <v>144</v>
+      </c>
+      <c r="E54" t="s">
+        <v>401</v>
+      </c>
+      <c r="F54" t="s">
+        <v>402</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>404</v>
+      </c>
+      <c r="B55" t="s">
+        <v>405</v>
+      </c>
+      <c r="C55" t="s">
+        <v>173</v>
+      </c>
+      <c r="D55" t="s">
+        <v>144</v>
+      </c>
+      <c r="E55" t="s">
+        <v>406</v>
+      </c>
+      <c r="F55" t="s">
+        <v>407</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>409</v>
+      </c>
+      <c r="B56" t="s">
+        <v>410</v>
+      </c>
+      <c r="C56" t="s">
+        <v>173</v>
+      </c>
+      <c r="D56" t="s">
+        <v>144</v>
+      </c>
+      <c r="E56" t="s">
+        <v>411</v>
+      </c>
+      <c r="F56" t="s">
+        <v>138</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>413</v>
+      </c>
+      <c r="B57" t="s">
+        <v>414</v>
+      </c>
+      <c r="C57" t="s">
+        <v>330</v>
+      </c>
+      <c r="D57" t="s">
+        <v>144</v>
+      </c>
+      <c r="E57" t="s">
+        <v>415</v>
+      </c>
+      <c r="F57" t="s">
+        <v>138</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>417</v>
+      </c>
+      <c r="B58" t="s">
+        <v>418</v>
+      </c>
+      <c r="C58" t="s">
+        <v>247</v>
+      </c>
+      <c r="D58" t="s">
+        <v>144</v>
+      </c>
+      <c r="E58" t="s">
+        <v>294</v>
+      </c>
+      <c r="F58" t="s">
+        <v>138</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>420</v>
+      </c>
+      <c r="B59" t="s">
+        <v>421</v>
+      </c>
+      <c r="C59" t="s">
+        <v>330</v>
+      </c>
+      <c r="D59" t="s">
+        <v>144</v>
+      </c>
+      <c r="E59" t="s">
+        <v>422</v>
+      </c>
+      <c r="F59" t="s">
+        <v>407</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>424</v>
+      </c>
+      <c r="B60" t="s">
+        <v>425</v>
+      </c>
+      <c r="C60" t="s">
+        <v>359</v>
+      </c>
+      <c r="D60" t="s">
+        <v>144</v>
+      </c>
+      <c r="E60" t="s">
+        <v>426</v>
+      </c>
+      <c r="F60" t="s">
+        <v>427</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>429</v>
+      </c>
+      <c r="B61" t="s">
+        <v>430</v>
+      </c>
+      <c r="C61" t="s">
+        <v>431</v>
+      </c>
+      <c r="D61" t="s">
         <v>162</v>
       </c>
-      <c r="D34" t="s">
-        <v>144</v>
-      </c>
-      <c r="E34" t="s">
-        <v>145</v>
-      </c>
-      <c r="F34" t="s">
-        <v>167</v>
-      </c>
-      <c r="H34" s="2" t="s">
-        <v>290</v>
+      <c r="E61" t="s">
+        <v>432</v>
+      </c>
+      <c r="F61" t="s">
+        <v>433</v>
+      </c>
+      <c r="H61" s="2" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>435</v>
+      </c>
+      <c r="B62" t="s">
+        <v>436</v>
+      </c>
+      <c r="C62" t="s">
+        <v>437</v>
+      </c>
+      <c r="D62" t="s">
+        <v>144</v>
+      </c>
+      <c r="E62" t="s">
+        <v>438</v>
+      </c>
+      <c r="F62" t="s">
+        <v>138</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>440</v>
+      </c>
+      <c r="B63" t="s">
+        <v>441</v>
+      </c>
+      <c r="C63" t="s">
+        <v>155</v>
+      </c>
+      <c r="D63" t="s">
+        <v>144</v>
+      </c>
+      <c r="E63" t="s">
+        <v>442</v>
+      </c>
+      <c r="F63" t="s">
+        <v>443</v>
+      </c>
+      <c r="H63" s="2" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>445</v>
+      </c>
+      <c r="B64" t="s">
+        <v>446</v>
+      </c>
+      <c r="C64" t="s">
+        <v>173</v>
+      </c>
+      <c r="D64" t="s">
+        <v>144</v>
+      </c>
+      <c r="E64" t="s">
+        <v>447</v>
+      </c>
+      <c r="F64" t="s">
+        <v>448</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>450</v>
+      </c>
+      <c r="B65" t="s">
+        <v>451</v>
+      </c>
+      <c r="C65" t="s">
+        <v>452</v>
+      </c>
+      <c r="D65" t="s">
+        <v>144</v>
+      </c>
+      <c r="E65" t="s">
+        <v>406</v>
+      </c>
+      <c r="F65" t="s">
+        <v>433</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>454</v>
+      </c>
+      <c r="B66" t="s">
+        <v>455</v>
+      </c>
+      <c r="C66" t="s">
+        <v>155</v>
+      </c>
+      <c r="D66" t="s">
+        <v>144</v>
+      </c>
+      <c r="E66" t="s">
+        <v>456</v>
+      </c>
+      <c r="F66" t="s">
+        <v>457</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>459</v>
+      </c>
+      <c r="B67" t="s">
+        <v>460</v>
+      </c>
+      <c r="C67" t="s">
+        <v>461</v>
+      </c>
+      <c r="D67" t="s">
+        <v>144</v>
+      </c>
+      <c r="E67" t="s">
+        <v>462</v>
+      </c>
+      <c r="F67" t="s">
+        <v>463</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>465</v>
+      </c>
+      <c r="B68" t="s">
+        <v>466</v>
+      </c>
+      <c r="C68" t="s">
+        <v>467</v>
+      </c>
+      <c r="D68" t="s">
+        <v>370</v>
+      </c>
+      <c r="E68" t="s">
+        <v>468</v>
+      </c>
+      <c r="F68" t="s">
+        <v>392</v>
+      </c>
+      <c r="H68" s="2" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>470</v>
+      </c>
+      <c r="B69" t="s">
+        <v>471</v>
+      </c>
+      <c r="C69" t="s">
+        <v>472</v>
+      </c>
+      <c r="D69" t="s">
+        <v>144</v>
+      </c>
+      <c r="E69" t="s">
+        <v>473</v>
+      </c>
+      <c r="F69" t="s">
+        <v>146</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>475</v>
+      </c>
+      <c r="B70" t="s">
+        <v>261</v>
+      </c>
+      <c r="C70" t="s">
+        <v>262</v>
+      </c>
+      <c r="D70" t="s">
+        <v>144</v>
+      </c>
+      <c r="E70" t="s">
+        <v>138</v>
+      </c>
+      <c r="F70" t="s">
+        <v>138</v>
+      </c>
+      <c r="H70" s="2" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>477</v>
+      </c>
+      <c r="B71" t="s">
+        <v>478</v>
+      </c>
+      <c r="C71" t="s">
+        <v>247</v>
+      </c>
+      <c r="D71" t="s">
+        <v>168</v>
+      </c>
+      <c r="E71" t="s">
+        <v>203</v>
+      </c>
+      <c r="F71" t="s">
+        <v>479</v>
+      </c>
+      <c r="H71" s="2" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>477</v>
+      </c>
+      <c r="B72" t="s">
+        <v>481</v>
+      </c>
+      <c r="C72" t="s">
+        <v>482</v>
+      </c>
+      <c r="D72" t="s">
+        <v>144</v>
+      </c>
+      <c r="E72" t="s">
+        <v>483</v>
+      </c>
+      <c r="F72" t="s">
+        <v>484</v>
+      </c>
+      <c r="H72" s="2" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>486</v>
+      </c>
+      <c r="B73" t="s">
+        <v>138</v>
+      </c>
+      <c r="C73" t="s">
+        <v>173</v>
+      </c>
+      <c r="D73" t="s">
+        <v>144</v>
+      </c>
+      <c r="E73" t="s">
+        <v>487</v>
+      </c>
+      <c r="F73" t="s">
+        <v>488</v>
+      </c>
+      <c r="H73" s="2" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>490</v>
+      </c>
+      <c r="B74" t="s">
+        <v>138</v>
+      </c>
+      <c r="C74" t="s">
+        <v>173</v>
+      </c>
+      <c r="D74" t="s">
+        <v>144</v>
+      </c>
+      <c r="E74" t="s">
+        <v>487</v>
+      </c>
+      <c r="F74" t="s">
+        <v>491</v>
+      </c>
+      <c r="H74" s="2" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>493</v>
+      </c>
+      <c r="B75" t="s">
+        <v>138</v>
+      </c>
+      <c r="C75" t="s">
+        <v>173</v>
+      </c>
+      <c r="D75" t="s">
+        <v>144</v>
+      </c>
+      <c r="E75" t="s">
+        <v>487</v>
+      </c>
+      <c r="F75" t="s">
+        <v>491</v>
+      </c>
+      <c r="H75" s="2" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>495</v>
+      </c>
+      <c r="B76" t="s">
+        <v>138</v>
+      </c>
+      <c r="C76" t="s">
+        <v>173</v>
+      </c>
+      <c r="D76" t="s">
+        <v>144</v>
+      </c>
+      <c r="E76" t="s">
+        <v>487</v>
+      </c>
+      <c r="F76" t="s">
+        <v>491</v>
+      </c>
+      <c r="H76" s="2" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>497</v>
+      </c>
+      <c r="B77" t="s">
+        <v>138</v>
+      </c>
+      <c r="C77" t="s">
+        <v>173</v>
+      </c>
+      <c r="D77" t="s">
+        <v>144</v>
+      </c>
+      <c r="E77" t="s">
+        <v>487</v>
+      </c>
+      <c r="F77" t="s">
+        <v>498</v>
+      </c>
+      <c r="H77" s="2" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>500</v>
+      </c>
+      <c r="B78" t="s">
+        <v>501</v>
+      </c>
+      <c r="C78" t="s">
+        <v>502</v>
+      </c>
+      <c r="D78" t="s">
+        <v>144</v>
+      </c>
+      <c r="E78" t="s">
+        <v>138</v>
+      </c>
+      <c r="F78" t="s">
+        <v>503</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>505</v>
+      </c>
+      <c r="B79" t="s">
+        <v>506</v>
+      </c>
+      <c r="C79" t="s">
+        <v>507</v>
+      </c>
+      <c r="D79" t="s">
+        <v>144</v>
+      </c>
+      <c r="E79" t="s">
+        <v>508</v>
+      </c>
+      <c r="F79" t="s">
+        <v>509</v>
+      </c>
+      <c r="H79" s="2" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>511</v>
+      </c>
+      <c r="B80" t="s">
+        <v>512</v>
+      </c>
+      <c r="C80" t="s">
+        <v>513</v>
+      </c>
+      <c r="D80" t="s">
+        <v>144</v>
+      </c>
+      <c r="E80" t="s">
+        <v>138</v>
+      </c>
+      <c r="F80" t="s">
+        <v>443</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>515</v>
+      </c>
+      <c r="B81" t="s">
+        <v>516</v>
+      </c>
+      <c r="C81" t="s">
+        <v>155</v>
+      </c>
+      <c r="D81" t="s">
+        <v>144</v>
+      </c>
+      <c r="E81" t="s">
+        <v>517</v>
+      </c>
+      <c r="F81" t="s">
+        <v>443</v>
+      </c>
+      <c r="H81" s="2" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>519</v>
+      </c>
+      <c r="B82" t="s">
+        <v>520</v>
+      </c>
+      <c r="C82" t="s">
+        <v>173</v>
+      </c>
+      <c r="D82" t="s">
+        <v>144</v>
+      </c>
+      <c r="E82" t="s">
+        <v>447</v>
+      </c>
+      <c r="F82" t="s">
+        <v>407</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>522</v>
+      </c>
+      <c r="B83" t="s">
+        <v>523</v>
+      </c>
+      <c r="C83" t="s">
+        <v>330</v>
+      </c>
+      <c r="D83" t="s">
+        <v>144</v>
+      </c>
+      <c r="E83" t="s">
+        <v>524</v>
+      </c>
+      <c r="F83" t="s">
+        <v>525</v>
+      </c>
+      <c r="H83" s="2" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>527</v>
+      </c>
+      <c r="B84" t="s">
+        <v>528</v>
+      </c>
+      <c r="C84" t="s">
+        <v>507</v>
+      </c>
+      <c r="D84" t="s">
+        <v>144</v>
+      </c>
+      <c r="E84" t="s">
+        <v>529</v>
+      </c>
+      <c r="F84" t="s">
+        <v>530</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>532</v>
+      </c>
+      <c r="B85" t="s">
+        <v>533</v>
+      </c>
+      <c r="C85" t="s">
+        <v>534</v>
+      </c>
+      <c r="D85" t="s">
+        <v>162</v>
+      </c>
+      <c r="E85" t="s">
+        <v>535</v>
+      </c>
+      <c r="F85" t="s">
+        <v>138</v>
+      </c>
+      <c r="H85" s="2" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>537</v>
+      </c>
+      <c r="B86" t="s">
+        <v>209</v>
+      </c>
+      <c r="C86" t="s">
+        <v>538</v>
+      </c>
+      <c r="D86" t="s">
+        <v>162</v>
+      </c>
+      <c r="E86" t="s">
+        <v>138</v>
+      </c>
+      <c r="F86" t="s">
+        <v>215</v>
+      </c>
+      <c r="H86" s="2" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>540</v>
+      </c>
+      <c r="B87" t="s">
+        <v>541</v>
+      </c>
+      <c r="C87" t="s">
+        <v>173</v>
+      </c>
+      <c r="D87" t="s">
+        <v>144</v>
+      </c>
+      <c r="E87" t="s">
+        <v>542</v>
+      </c>
+      <c r="F87" t="s">
+        <v>543</v>
+      </c>
+      <c r="H87" s="2" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>545</v>
+      </c>
+      <c r="B88" t="s">
+        <v>546</v>
+      </c>
+      <c r="C88" t="s">
+        <v>314</v>
+      </c>
+      <c r="D88" t="s">
+        <v>144</v>
+      </c>
+      <c r="E88" t="s">
+        <v>360</v>
+      </c>
+      <c r="F88" t="s">
+        <v>547</v>
+      </c>
+      <c r="H88" s="2" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>549</v>
+      </c>
+      <c r="B89" t="s">
+        <v>550</v>
+      </c>
+      <c r="C89" t="s">
+        <v>359</v>
+      </c>
+      <c r="D89" t="s">
+        <v>144</v>
+      </c>
+      <c r="E89" t="s">
+        <v>551</v>
+      </c>
+      <c r="F89" t="s">
+        <v>138</v>
+      </c>
+      <c r="H89" s="2" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>553</v>
+      </c>
+      <c r="B90" t="s">
+        <v>506</v>
+      </c>
+      <c r="C90" t="s">
+        <v>507</v>
+      </c>
+      <c r="D90" t="s">
+        <v>144</v>
+      </c>
+      <c r="E90" t="s">
+        <v>554</v>
+      </c>
+      <c r="F90" t="s">
+        <v>555</v>
+      </c>
+      <c r="H90" s="2" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>557</v>
+      </c>
+      <c r="B91" t="s">
+        <v>558</v>
+      </c>
+      <c r="C91" t="s">
+        <v>359</v>
+      </c>
+      <c r="D91" t="s">
+        <v>144</v>
+      </c>
+      <c r="E91" t="s">
+        <v>559</v>
+      </c>
+      <c r="F91" t="s">
+        <v>138</v>
+      </c>
+      <c r="H91" s="2" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>561</v>
+      </c>
+      <c r="B92" t="s">
+        <v>562</v>
+      </c>
+      <c r="C92" t="s">
+        <v>563</v>
+      </c>
+      <c r="D92" t="s">
+        <v>144</v>
+      </c>
+      <c r="E92" t="s">
+        <v>564</v>
+      </c>
+      <c r="F92" t="s">
+        <v>565</v>
+      </c>
+      <c r="H92" s="2" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>567</v>
+      </c>
+      <c r="B93" t="s">
+        <v>568</v>
+      </c>
+      <c r="C93" t="s">
+        <v>569</v>
+      </c>
+      <c r="D93" t="s">
+        <v>144</v>
+      </c>
+      <c r="E93" t="s">
+        <v>570</v>
+      </c>
+      <c r="F93" t="s">
+        <v>571</v>
+      </c>
+      <c r="H93" s="2" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>573</v>
+      </c>
+      <c r="B94" t="s">
+        <v>528</v>
+      </c>
+      <c r="C94" t="s">
+        <v>507</v>
+      </c>
+      <c r="D94" t="s">
+        <v>144</v>
+      </c>
+      <c r="E94" t="s">
+        <v>574</v>
+      </c>
+      <c r="F94" t="s">
+        <v>575</v>
+      </c>
+      <c r="H94" s="2" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>577</v>
+      </c>
+      <c r="B95" t="s">
+        <v>578</v>
+      </c>
+      <c r="C95" t="s">
+        <v>155</v>
+      </c>
+      <c r="D95" t="s">
+        <v>144</v>
+      </c>
+      <c r="E95" t="s">
+        <v>579</v>
+      </c>
+      <c r="F95" t="s">
+        <v>433</v>
+      </c>
+      <c r="H95" s="2" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>581</v>
+      </c>
+      <c r="B96" t="s">
+        <v>582</v>
+      </c>
+      <c r="C96" t="s">
+        <v>247</v>
+      </c>
+      <c r="D96" t="s">
+        <v>144</v>
+      </c>
+      <c r="E96" t="s">
+        <v>583</v>
+      </c>
+      <c r="F96" t="s">
+        <v>584</v>
+      </c>
+      <c r="H96" s="2" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>586</v>
+      </c>
+      <c r="B97" t="s">
+        <v>587</v>
+      </c>
+      <c r="C97" t="s">
+        <v>330</v>
+      </c>
+      <c r="D97" t="s">
+        <v>144</v>
+      </c>
+      <c r="E97" t="s">
+        <v>588</v>
+      </c>
+      <c r="F97" t="s">
+        <v>589</v>
+      </c>
+      <c r="H97" s="2" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>591</v>
+      </c>
+      <c r="B98" t="s">
+        <v>441</v>
+      </c>
+      <c r="C98" t="s">
+        <v>155</v>
+      </c>
+      <c r="D98" t="s">
+        <v>144</v>
+      </c>
+      <c r="E98" t="s">
+        <v>554</v>
+      </c>
+      <c r="F98" t="s">
+        <v>443</v>
+      </c>
+      <c r="H98" s="2" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>593</v>
+      </c>
+      <c r="B99" t="s">
+        <v>594</v>
+      </c>
+      <c r="C99" t="s">
+        <v>472</v>
+      </c>
+      <c r="D99" t="s">
+        <v>144</v>
+      </c>
+      <c r="E99" t="s">
+        <v>156</v>
+      </c>
+      <c r="F99" t="s">
+        <v>138</v>
+      </c>
+      <c r="H99" s="2" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>596</v>
+      </c>
+      <c r="B100" t="s">
+        <v>597</v>
+      </c>
+      <c r="C100" t="s">
+        <v>598</v>
+      </c>
+      <c r="D100" t="s">
+        <v>144</v>
+      </c>
+      <c r="E100" t="s">
+        <v>599</v>
+      </c>
+      <c r="F100" t="s">
+        <v>600</v>
+      </c>
+      <c r="H100" s="2" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>602</v>
+      </c>
+      <c r="B101" t="s">
+        <v>603</v>
+      </c>
+      <c r="C101" t="s">
+        <v>604</v>
+      </c>
+      <c r="D101" t="s">
+        <v>144</v>
+      </c>
+      <c r="E101" t="s">
+        <v>315</v>
+      </c>
+      <c r="F101" t="s">
+        <v>605</v>
+      </c>
+      <c r="H101" s="2" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>607</v>
+      </c>
+      <c r="B102" t="s">
+        <v>608</v>
+      </c>
+      <c r="C102" t="s">
+        <v>609</v>
+      </c>
+      <c r="D102" t="s">
+        <v>144</v>
+      </c>
+      <c r="E102" t="s">
+        <v>610</v>
+      </c>
+      <c r="F102" t="s">
+        <v>611</v>
+      </c>
+      <c r="H102" s="2" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>613</v>
+      </c>
+      <c r="B103" t="s">
+        <v>614</v>
+      </c>
+      <c r="C103" t="s">
+        <v>173</v>
+      </c>
+      <c r="D103" t="s">
+        <v>144</v>
+      </c>
+      <c r="E103" t="s">
+        <v>615</v>
+      </c>
+      <c r="F103" t="s">
+        <v>138</v>
+      </c>
+      <c r="H103" s="2" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>617</v>
+      </c>
+      <c r="B104" t="s">
+        <v>618</v>
+      </c>
+      <c r="C104" t="s">
+        <v>619</v>
+      </c>
+      <c r="D104" t="s">
+        <v>202</v>
+      </c>
+      <c r="E104" t="s">
+        <v>203</v>
+      </c>
+      <c r="F104" t="s">
+        <v>620</v>
+      </c>
+      <c r="H104" s="2" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>622</v>
+      </c>
+      <c r="B105" t="s">
+        <v>623</v>
+      </c>
+      <c r="C105" t="s">
+        <v>624</v>
+      </c>
+      <c r="D105" t="s">
+        <v>162</v>
+      </c>
+      <c r="E105" t="s">
+        <v>625</v>
+      </c>
+      <c r="F105" t="s">
+        <v>626</v>
+      </c>
+      <c r="H105" s="2" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>628</v>
+      </c>
+      <c r="B106" t="s">
+        <v>292</v>
+      </c>
+      <c r="C106" t="s">
+        <v>293</v>
+      </c>
+      <c r="D106" t="s">
+        <v>162</v>
+      </c>
+      <c r="E106" t="s">
+        <v>629</v>
+      </c>
+      <c r="F106" t="s">
+        <v>295</v>
+      </c>
+      <c r="H106" s="2" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>631</v>
+      </c>
+      <c r="B107" t="s">
+        <v>632</v>
+      </c>
+      <c r="C107" t="s">
+        <v>299</v>
+      </c>
+      <c r="D107" t="s">
+        <v>144</v>
+      </c>
+      <c r="E107" t="s">
+        <v>633</v>
+      </c>
+      <c r="F107" t="s">
+        <v>138</v>
+      </c>
+      <c r="H107" s="2" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>635</v>
+      </c>
+      <c r="B108" t="s">
+        <v>636</v>
+      </c>
+      <c r="C108" t="s">
+        <v>247</v>
+      </c>
+      <c r="D108" t="s">
+        <v>144</v>
+      </c>
+      <c r="E108" t="s">
+        <v>637</v>
+      </c>
+      <c r="F108" t="s">
+        <v>638</v>
+      </c>
+      <c r="H108" s="2" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>640</v>
+      </c>
+      <c r="B109" t="s">
+        <v>641</v>
+      </c>
+      <c r="C109" t="s">
+        <v>258</v>
+      </c>
+      <c r="D109" t="s">
+        <v>144</v>
+      </c>
+      <c r="E109" t="s">
+        <v>642</v>
+      </c>
+      <c r="F109" t="s">
+        <v>643</v>
+      </c>
+      <c r="H109" s="2" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>645</v>
+      </c>
+      <c r="B110" t="s">
+        <v>646</v>
+      </c>
+      <c r="C110" t="s">
+        <v>155</v>
+      </c>
+      <c r="D110" t="s">
+        <v>144</v>
+      </c>
+      <c r="E110" t="s">
+        <v>647</v>
+      </c>
+      <c r="F110" t="s">
+        <v>648</v>
+      </c>
+      <c r="H110" s="2" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>650</v>
+      </c>
+      <c r="B111" t="s">
+        <v>636</v>
+      </c>
+      <c r="C111" t="s">
+        <v>247</v>
+      </c>
+      <c r="D111" t="s">
+        <v>144</v>
+      </c>
+      <c r="E111" t="s">
+        <v>651</v>
+      </c>
+      <c r="F111" t="s">
+        <v>638</v>
+      </c>
+      <c r="H111" s="2" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>653</v>
+      </c>
+      <c r="B112" t="s">
+        <v>654</v>
+      </c>
+      <c r="C112" t="s">
+        <v>155</v>
+      </c>
+      <c r="D112" t="s">
+        <v>144</v>
+      </c>
+      <c r="E112" t="s">
+        <v>655</v>
+      </c>
+      <c r="F112" t="s">
+        <v>185</v>
+      </c>
+      <c r="H112" s="2" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>657</v>
+      </c>
+      <c r="B113" t="s">
+        <v>658</v>
+      </c>
+      <c r="C113" t="s">
+        <v>219</v>
+      </c>
+      <c r="D113" t="s">
+        <v>162</v>
+      </c>
+      <c r="E113" t="s">
+        <v>659</v>
+      </c>
+      <c r="F113" t="s">
+        <v>660</v>
+      </c>
+      <c r="H113" s="2" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>662</v>
+      </c>
+      <c r="B114" t="s">
+        <v>663</v>
+      </c>
+      <c r="C114" t="s">
+        <v>664</v>
+      </c>
+      <c r="D114" t="s">
+        <v>144</v>
+      </c>
+      <c r="E114" t="s">
+        <v>138</v>
+      </c>
+      <c r="F114" t="s">
+        <v>138</v>
+      </c>
+      <c r="H114" s="2" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>666</v>
+      </c>
+      <c r="B115" t="s">
+        <v>667</v>
+      </c>
+      <c r="C115" t="s">
+        <v>299</v>
+      </c>
+      <c r="D115" t="s">
+        <v>162</v>
+      </c>
+      <c r="E115" t="s">
+        <v>668</v>
+      </c>
+      <c r="F115" t="s">
+        <v>669</v>
+      </c>
+      <c r="H115" s="2" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>671</v>
+      </c>
+      <c r="B116" t="s">
+        <v>672</v>
+      </c>
+      <c r="C116" t="s">
+        <v>247</v>
+      </c>
+      <c r="D116" t="s">
+        <v>168</v>
+      </c>
+      <c r="E116" t="s">
+        <v>673</v>
+      </c>
+      <c r="F116" t="s">
+        <v>674</v>
+      </c>
+      <c r="H116" s="2" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>676</v>
+      </c>
+      <c r="B117" t="s">
+        <v>481</v>
+      </c>
+      <c r="C117" t="s">
+        <v>482</v>
+      </c>
+      <c r="D117" t="s">
+        <v>144</v>
+      </c>
+      <c r="E117" t="s">
+        <v>677</v>
+      </c>
+      <c r="F117" t="s">
+        <v>484</v>
+      </c>
+      <c r="H117" s="2" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>679</v>
+      </c>
+      <c r="B118" t="s">
+        <v>680</v>
+      </c>
+      <c r="C118" t="s">
+        <v>330</v>
+      </c>
+      <c r="D118" t="s">
+        <v>162</v>
+      </c>
+      <c r="E118" t="s">
+        <v>138</v>
+      </c>
+      <c r="F118" t="s">
+        <v>138</v>
+      </c>
+      <c r="H118" s="2" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>682</v>
+      </c>
+      <c r="B119" t="s">
+        <v>683</v>
+      </c>
+      <c r="C119" t="s">
+        <v>684</v>
+      </c>
+      <c r="D119" t="s">
+        <v>144</v>
+      </c>
+      <c r="E119" t="s">
+        <v>685</v>
+      </c>
+      <c r="F119" t="s">
+        <v>281</v>
+      </c>
+      <c r="H119" s="2" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>687</v>
+      </c>
+      <c r="B120" t="s">
+        <v>209</v>
+      </c>
+      <c r="C120" t="s">
+        <v>214</v>
+      </c>
+      <c r="D120" t="s">
+        <v>168</v>
+      </c>
+      <c r="E120" t="s">
+        <v>138</v>
+      </c>
+      <c r="F120" t="s">
+        <v>285</v>
+      </c>
+      <c r="H120" s="2" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>689</v>
+      </c>
+      <c r="B121" t="s">
+        <v>690</v>
+      </c>
+      <c r="C121" t="s">
+        <v>691</v>
+      </c>
+      <c r="D121" t="s">
+        <v>144</v>
+      </c>
+      <c r="E121" t="s">
+        <v>692</v>
+      </c>
+      <c r="F121" t="s">
+        <v>693</v>
+      </c>
+      <c r="H121" s="2" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>695</v>
+      </c>
+      <c r="B122" t="s">
+        <v>696</v>
+      </c>
+      <c r="C122" t="s">
+        <v>697</v>
+      </c>
+      <c r="D122" t="s">
+        <v>144</v>
+      </c>
+      <c r="E122" t="s">
+        <v>698</v>
+      </c>
+      <c r="F122" t="s">
+        <v>699</v>
+      </c>
+      <c r="H122" s="2" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>701</v>
+      </c>
+      <c r="B123" t="s">
+        <v>702</v>
+      </c>
+      <c r="C123" t="s">
+        <v>359</v>
+      </c>
+      <c r="D123" t="s">
+        <v>144</v>
+      </c>
+      <c r="E123" t="s">
+        <v>703</v>
+      </c>
+      <c r="F123" t="s">
+        <v>704</v>
+      </c>
+      <c r="H123" s="2" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>706</v>
+      </c>
+      <c r="B124" t="s">
+        <v>696</v>
+      </c>
+      <c r="C124" t="s">
+        <v>707</v>
+      </c>
+      <c r="D124" t="s">
+        <v>144</v>
+      </c>
+      <c r="E124" t="s">
+        <v>554</v>
+      </c>
+      <c r="F124" t="s">
+        <v>699</v>
+      </c>
+      <c r="H124" s="2" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>709</v>
+      </c>
+      <c r="B125" t="s">
+        <v>710</v>
+      </c>
+      <c r="C125" t="s">
+        <v>472</v>
+      </c>
+      <c r="D125" t="s">
+        <v>162</v>
+      </c>
+      <c r="E125" t="s">
+        <v>711</v>
+      </c>
+      <c r="F125" t="s">
+        <v>712</v>
+      </c>
+      <c r="H125" s="2" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>714</v>
+      </c>
+      <c r="B126" t="s">
+        <v>715</v>
+      </c>
+      <c r="C126" t="s">
+        <v>299</v>
+      </c>
+      <c r="D126" t="s">
+        <v>144</v>
+      </c>
+      <c r="E126" t="s">
+        <v>716</v>
+      </c>
+      <c r="F126" t="s">
+        <v>717</v>
+      </c>
+      <c r="H126" s="2" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>719</v>
+      </c>
+      <c r="B127" t="s">
+        <v>720</v>
+      </c>
+      <c r="C127" t="s">
+        <v>299</v>
+      </c>
+      <c r="D127" t="s">
+        <v>144</v>
+      </c>
+      <c r="E127" t="s">
+        <v>721</v>
+      </c>
+      <c r="F127" t="s">
+        <v>722</v>
+      </c>
+      <c r="H127" s="2" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>724</v>
+      </c>
+      <c r="B128" t="s">
+        <v>725</v>
+      </c>
+      <c r="C128" t="s">
+        <v>726</v>
+      </c>
+      <c r="D128" t="s">
+        <v>144</v>
+      </c>
+      <c r="E128" t="s">
+        <v>642</v>
+      </c>
+      <c r="F128" t="s">
+        <v>727</v>
+      </c>
+      <c r="H128" s="2" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>729</v>
+      </c>
+      <c r="B129" t="s">
+        <v>730</v>
+      </c>
+      <c r="C129" t="s">
+        <v>359</v>
+      </c>
+      <c r="D129" t="s">
+        <v>144</v>
+      </c>
+      <c r="E129" t="s">
+        <v>731</v>
+      </c>
+      <c r="F129" t="s">
+        <v>138</v>
+      </c>
+      <c r="H129" s="2" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>733</v>
+      </c>
+      <c r="B130" t="s">
+        <v>730</v>
+      </c>
+      <c r="C130" t="s">
+        <v>359</v>
+      </c>
+      <c r="D130" t="s">
+        <v>144</v>
+      </c>
+      <c r="E130" t="s">
+        <v>731</v>
+      </c>
+      <c r="F130" t="s">
+        <v>138</v>
+      </c>
+      <c r="H130" s="2" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>735</v>
+      </c>
+      <c r="B131" t="s">
+        <v>736</v>
+      </c>
+      <c r="C131" t="s">
+        <v>737</v>
+      </c>
+      <c r="D131" t="s">
+        <v>144</v>
+      </c>
+      <c r="E131" t="s">
+        <v>738</v>
+      </c>
+      <c r="F131" t="s">
+        <v>407</v>
+      </c>
+      <c r="H131" s="2" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>740</v>
+      </c>
+      <c r="B132" t="s">
+        <v>138</v>
+      </c>
+      <c r="C132" t="s">
+        <v>741</v>
+      </c>
+      <c r="D132" t="s">
+        <v>144</v>
+      </c>
+      <c r="E132" t="s">
+        <v>742</v>
+      </c>
+      <c r="F132" t="s">
+        <v>743</v>
+      </c>
+      <c r="H132" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>745</v>
+      </c>
+      <c r="B133" t="s">
+        <v>746</v>
+      </c>
+      <c r="C133" t="s">
+        <v>247</v>
+      </c>
+      <c r="D133" t="s">
+        <v>144</v>
+      </c>
+      <c r="E133" t="s">
+        <v>747</v>
+      </c>
+      <c r="F133" t="s">
+        <v>138</v>
+      </c>
+      <c r="H133" s="2" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>749</v>
+      </c>
+      <c r="B134" t="s">
+        <v>636</v>
+      </c>
+      <c r="C134" t="s">
+        <v>247</v>
+      </c>
+      <c r="D134" t="s">
+        <v>144</v>
+      </c>
+      <c r="E134" t="s">
+        <v>750</v>
+      </c>
+      <c r="F134" t="s">
+        <v>638</v>
+      </c>
+      <c r="H134" s="2" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>752</v>
+      </c>
+      <c r="B135" t="s">
+        <v>142</v>
+      </c>
+      <c r="C135" t="s">
+        <v>247</v>
+      </c>
+      <c r="D135" t="s">
+        <v>162</v>
+      </c>
+      <c r="E135" t="s">
+        <v>753</v>
+      </c>
+      <c r="F135" t="s">
+        <v>146</v>
+      </c>
+      <c r="H135" s="2" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>755</v>
+      </c>
+      <c r="B136" t="s">
+        <v>756</v>
+      </c>
+      <c r="C136" t="s">
+        <v>757</v>
+      </c>
+      <c r="D136" t="s">
+        <v>144</v>
+      </c>
+      <c r="E136" t="s">
+        <v>758</v>
+      </c>
+      <c r="F136" t="s">
+        <v>759</v>
+      </c>
+      <c r="H136" s="2" t="s">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>761</v>
+      </c>
+      <c r="B137" t="s">
+        <v>762</v>
+      </c>
+      <c r="C137" t="s">
+        <v>173</v>
+      </c>
+      <c r="D137" t="s">
+        <v>144</v>
+      </c>
+      <c r="E137" t="s">
+        <v>633</v>
+      </c>
+      <c r="F137" t="s">
+        <v>763</v>
+      </c>
+      <c r="H137" s="2" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>765</v>
+      </c>
+      <c r="B138" t="s">
+        <v>766</v>
+      </c>
+      <c r="C138" t="s">
+        <v>173</v>
+      </c>
+      <c r="D138" t="s">
+        <v>370</v>
+      </c>
+      <c r="E138" t="s">
+        <v>767</v>
+      </c>
+      <c r="F138" t="s">
+        <v>138</v>
+      </c>
+      <c r="H138" s="2" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>769</v>
+      </c>
+      <c r="B139" t="s">
+        <v>770</v>
+      </c>
+      <c r="C139" t="s">
+        <v>247</v>
+      </c>
+      <c r="D139" t="s">
+        <v>168</v>
+      </c>
+      <c r="E139" t="s">
+        <v>771</v>
+      </c>
+      <c r="F139" t="s">
+        <v>772</v>
+      </c>
+      <c r="H139" s="2" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>774</v>
+      </c>
+      <c r="B140" t="s">
+        <v>725</v>
+      </c>
+      <c r="C140" t="s">
+        <v>726</v>
+      </c>
+      <c r="D140" t="s">
+        <v>144</v>
+      </c>
+      <c r="E140" t="s">
+        <v>775</v>
+      </c>
+      <c r="F140" t="s">
+        <v>727</v>
+      </c>
+      <c r="H140" s="2" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>777</v>
+      </c>
+      <c r="B141" t="s">
+        <v>778</v>
+      </c>
+      <c r="C141" t="s">
+        <v>779</v>
+      </c>
+      <c r="D141" t="s">
+        <v>144</v>
+      </c>
+      <c r="E141" t="s">
+        <v>780</v>
+      </c>
+      <c r="F141" t="s">
+        <v>781</v>
+      </c>
+      <c r="H141" s="2" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>783</v>
+      </c>
+      <c r="B142" t="s">
+        <v>730</v>
+      </c>
+      <c r="C142" t="s">
+        <v>359</v>
+      </c>
+      <c r="D142" t="s">
+        <v>144</v>
+      </c>
+      <c r="E142" t="s">
+        <v>731</v>
+      </c>
+      <c r="F142" t="s">
+        <v>138</v>
+      </c>
+      <c r="H142" s="2" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>785</v>
+      </c>
+      <c r="B143" t="s">
+        <v>268</v>
+      </c>
+      <c r="C143" t="s">
+        <v>247</v>
+      </c>
+      <c r="D143" t="s">
+        <v>144</v>
+      </c>
+      <c r="E143" t="s">
+        <v>786</v>
+      </c>
+      <c r="F143" t="s">
+        <v>270</v>
+      </c>
+      <c r="H143" s="2" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>788</v>
+      </c>
+      <c r="B144" t="s">
+        <v>789</v>
+      </c>
+      <c r="C144" t="s">
+        <v>299</v>
+      </c>
+      <c r="D144" t="s">
+        <v>144</v>
+      </c>
+      <c r="E144" t="s">
+        <v>790</v>
+      </c>
+      <c r="F144" t="s">
+        <v>791</v>
+      </c>
+      <c r="H144" s="2" t="s">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>793</v>
+      </c>
+      <c r="B145" t="s">
+        <v>481</v>
+      </c>
+      <c r="C145" t="s">
+        <v>794</v>
+      </c>
+      <c r="D145" t="s">
+        <v>144</v>
+      </c>
+      <c r="E145" t="s">
+        <v>795</v>
+      </c>
+      <c r="F145" t="s">
+        <v>484</v>
+      </c>
+      <c r="H145" s="2" t="s">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>797</v>
+      </c>
+      <c r="B146" t="s">
+        <v>798</v>
+      </c>
+      <c r="C146" t="s">
+        <v>707</v>
+      </c>
+      <c r="D146" t="s">
+        <v>144</v>
+      </c>
+      <c r="E146" t="s">
+        <v>564</v>
+      </c>
+      <c r="F146" t="s">
+        <v>600</v>
+      </c>
+      <c r="H146" s="2" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>800</v>
+      </c>
+      <c r="B147" t="s">
+        <v>801</v>
+      </c>
+      <c r="C147" t="s">
+        <v>802</v>
+      </c>
+      <c r="D147" t="s">
+        <v>144</v>
+      </c>
+      <c r="E147" t="s">
+        <v>803</v>
+      </c>
+      <c r="F147" t="s">
+        <v>804</v>
+      </c>
+      <c r="H147" s="2" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>800</v>
+      </c>
+      <c r="B148" t="s">
+        <v>806</v>
+      </c>
+      <c r="C148" t="s">
+        <v>173</v>
+      </c>
+      <c r="D148" t="s">
+        <v>370</v>
+      </c>
+      <c r="E148" t="s">
+        <v>647</v>
+      </c>
+      <c r="F148" t="s">
+        <v>407</v>
+      </c>
+      <c r="H148" s="2" t="s">
+        <v>807</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>808</v>
+      </c>
+      <c r="B149" t="s">
+        <v>809</v>
+      </c>
+      <c r="C149" t="s">
+        <v>810</v>
+      </c>
+      <c r="D149" t="s">
+        <v>144</v>
+      </c>
+      <c r="E149" t="s">
+        <v>811</v>
+      </c>
+      <c r="F149" t="s">
+        <v>812</v>
+      </c>
+      <c r="H149" s="2" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>814</v>
+      </c>
+      <c r="B150" t="s">
+        <v>815</v>
+      </c>
+      <c r="C150" t="s">
+        <v>757</v>
+      </c>
+      <c r="D150" t="s">
+        <v>144</v>
+      </c>
+      <c r="E150" t="s">
+        <v>816</v>
+      </c>
+      <c r="F150" t="s">
+        <v>817</v>
+      </c>
+      <c r="H150" s="2" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>819</v>
+      </c>
+      <c r="B151" t="s">
+        <v>820</v>
+      </c>
+      <c r="C151" t="s">
+        <v>821</v>
+      </c>
+      <c r="D151" t="s">
+        <v>144</v>
+      </c>
+      <c r="E151" t="s">
+        <v>822</v>
+      </c>
+      <c r="F151" t="s">
+        <v>823</v>
+      </c>
+      <c r="H151" s="2" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>825</v>
+      </c>
+      <c r="B152" t="s">
+        <v>826</v>
+      </c>
+      <c r="C152" t="s">
+        <v>472</v>
+      </c>
+      <c r="D152" t="s">
+        <v>144</v>
+      </c>
+      <c r="E152" t="s">
+        <v>827</v>
+      </c>
+      <c r="F152" t="s">
+        <v>828</v>
+      </c>
+      <c r="H152" s="2" t="s">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>830</v>
+      </c>
+      <c r="B153" t="s">
+        <v>831</v>
+      </c>
+      <c r="C153" t="s">
+        <v>219</v>
+      </c>
+      <c r="D153" t="s">
+        <v>144</v>
+      </c>
+      <c r="E153" t="s">
+        <v>832</v>
+      </c>
+      <c r="F153" t="s">
+        <v>833</v>
+      </c>
+      <c r="H153" s="2" t="s">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>835</v>
+      </c>
+      <c r="B154" t="s">
+        <v>481</v>
+      </c>
+      <c r="C154" t="s">
+        <v>482</v>
+      </c>
+      <c r="D154" t="s">
+        <v>144</v>
+      </c>
+      <c r="E154" t="s">
+        <v>836</v>
+      </c>
+      <c r="F154" t="s">
+        <v>484</v>
+      </c>
+      <c r="H154" s="2" t="s">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>838</v>
+      </c>
+      <c r="B155" t="s">
+        <v>839</v>
+      </c>
+      <c r="C155" t="s">
+        <v>314</v>
+      </c>
+      <c r="D155" t="s">
+        <v>168</v>
+      </c>
+      <c r="E155" t="s">
+        <v>840</v>
+      </c>
+      <c r="F155" t="s">
+        <v>841</v>
+      </c>
+      <c r="H155" s="2" t="s">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>843</v>
+      </c>
+      <c r="B156" t="s">
+        <v>528</v>
+      </c>
+      <c r="C156" t="s">
+        <v>507</v>
+      </c>
+      <c r="D156" t="s">
+        <v>144</v>
+      </c>
+      <c r="E156" t="s">
+        <v>844</v>
+      </c>
+      <c r="F156" t="s">
+        <v>845</v>
+      </c>
+      <c r="H156" s="2" t="s">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>847</v>
+      </c>
+      <c r="B157" t="s">
+        <v>778</v>
+      </c>
+      <c r="C157" t="s">
+        <v>779</v>
+      </c>
+      <c r="D157" t="s">
+        <v>144</v>
+      </c>
+      <c r="E157" t="s">
+        <v>848</v>
+      </c>
+      <c r="F157" t="s">
+        <v>781</v>
+      </c>
+      <c r="H157" s="2" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>850</v>
+      </c>
+      <c r="B158" t="s">
+        <v>851</v>
+      </c>
+      <c r="C158" t="s">
+        <v>247</v>
+      </c>
+      <c r="D158" t="s">
+        <v>144</v>
+      </c>
+      <c r="E158" t="s">
+        <v>852</v>
+      </c>
+      <c r="F158" t="s">
+        <v>853</v>
+      </c>
+      <c r="H158" s="2" t="s">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="159" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>855</v>
+      </c>
+      <c r="B159" t="s">
+        <v>856</v>
+      </c>
+      <c r="C159" t="s">
+        <v>247</v>
+      </c>
+      <c r="D159" t="s">
+        <v>144</v>
+      </c>
+      <c r="E159" t="s">
+        <v>857</v>
+      </c>
+      <c r="F159" t="s">
+        <v>858</v>
+      </c>
+      <c r="H159" s="2" t="s">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="160" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>860</v>
+      </c>
+      <c r="B160" t="s">
+        <v>861</v>
+      </c>
+      <c r="C160" t="s">
+        <v>247</v>
+      </c>
+      <c r="D160" t="s">
+        <v>144</v>
+      </c>
+      <c r="E160" t="s">
+        <v>138</v>
+      </c>
+      <c r="F160" t="s">
+        <v>812</v>
+      </c>
+      <c r="H160" s="2" t="s">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="161" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>863</v>
+      </c>
+      <c r="B161" t="s">
+        <v>481</v>
+      </c>
+      <c r="C161" t="s">
+        <v>482</v>
+      </c>
+      <c r="D161" t="s">
+        <v>144</v>
+      </c>
+      <c r="E161" t="s">
+        <v>864</v>
+      </c>
+      <c r="F161" t="s">
+        <v>484</v>
+      </c>
+      <c r="H161" s="2" t="s">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="162" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>866</v>
+      </c>
+      <c r="B162" t="s">
+        <v>405</v>
+      </c>
+      <c r="C162" t="s">
+        <v>173</v>
+      </c>
+      <c r="D162" t="s">
+        <v>144</v>
+      </c>
+      <c r="E162" t="s">
+        <v>867</v>
+      </c>
+      <c r="F162" t="s">
+        <v>407</v>
+      </c>
+      <c r="H162" s="2" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="163" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>869</v>
+      </c>
+      <c r="B163" t="s">
+        <v>405</v>
+      </c>
+      <c r="C163" t="s">
+        <v>173</v>
+      </c>
+      <c r="D163" t="s">
+        <v>144</v>
+      </c>
+      <c r="E163" t="s">
+        <v>867</v>
+      </c>
+      <c r="F163" t="s">
+        <v>407</v>
+      </c>
+      <c r="H163" s="2" t="s">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="164" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
+        <v>871</v>
+      </c>
+      <c r="B164" t="s">
+        <v>872</v>
+      </c>
+      <c r="C164" t="s">
+        <v>173</v>
+      </c>
+      <c r="D164" t="s">
+        <v>202</v>
+      </c>
+      <c r="E164" t="s">
+        <v>203</v>
+      </c>
+      <c r="F164" t="s">
+        <v>281</v>
+      </c>
+      <c r="H164" s="2" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="165" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
+        <v>874</v>
+      </c>
+      <c r="B165" t="s">
+        <v>209</v>
+      </c>
+      <c r="C165" t="s">
+        <v>210</v>
+      </c>
+      <c r="D165" t="s">
+        <v>162</v>
+      </c>
+      <c r="E165" t="s">
+        <v>138</v>
+      </c>
+      <c r="F165" t="s">
+        <v>215</v>
+      </c>
+      <c r="H165" s="2" t="s">
+        <v>875</v>
       </c>
     </row>
   </sheetData>
@@ -2732,6 +7526,137 @@
     <hyperlink ref="H32" r:id="rId31"/>
     <hyperlink ref="H33" r:id="rId32"/>
     <hyperlink ref="H34" r:id="rId33"/>
+    <hyperlink ref="H35" r:id="rId34"/>
+    <hyperlink ref="H36" r:id="rId35"/>
+    <hyperlink ref="H37" r:id="rId36"/>
+    <hyperlink ref="H38" r:id="rId37"/>
+    <hyperlink ref="H39" r:id="rId38"/>
+    <hyperlink ref="H40" r:id="rId39"/>
+    <hyperlink ref="H41" r:id="rId40"/>
+    <hyperlink ref="H42" r:id="rId41"/>
+    <hyperlink ref="H43" r:id="rId42"/>
+    <hyperlink ref="H44" r:id="rId43"/>
+    <hyperlink ref="H45" r:id="rId44"/>
+    <hyperlink ref="H46" r:id="rId45"/>
+    <hyperlink ref="H47" r:id="rId46"/>
+    <hyperlink ref="H48" r:id="rId47"/>
+    <hyperlink ref="H49" r:id="rId48"/>
+    <hyperlink ref="H50" r:id="rId49"/>
+    <hyperlink ref="H51" r:id="rId50"/>
+    <hyperlink ref="H52" r:id="rId51"/>
+    <hyperlink ref="H53" r:id="rId52"/>
+    <hyperlink ref="H54" r:id="rId53"/>
+    <hyperlink ref="H55" r:id="rId54"/>
+    <hyperlink ref="H56" r:id="rId55"/>
+    <hyperlink ref="H57" r:id="rId56"/>
+    <hyperlink ref="H58" r:id="rId57"/>
+    <hyperlink ref="H59" r:id="rId58"/>
+    <hyperlink ref="H60" r:id="rId59"/>
+    <hyperlink ref="H61" r:id="rId60"/>
+    <hyperlink ref="H62" r:id="rId61"/>
+    <hyperlink ref="H63" r:id="rId62"/>
+    <hyperlink ref="H64" r:id="rId63"/>
+    <hyperlink ref="H65" r:id="rId64"/>
+    <hyperlink ref="H66" r:id="rId65"/>
+    <hyperlink ref="H67" r:id="rId66"/>
+    <hyperlink ref="H68" r:id="rId67"/>
+    <hyperlink ref="H69" r:id="rId68"/>
+    <hyperlink ref="H70" r:id="rId69"/>
+    <hyperlink ref="H71" r:id="rId70"/>
+    <hyperlink ref="H72" r:id="rId71"/>
+    <hyperlink ref="H73" r:id="rId72"/>
+    <hyperlink ref="H74" r:id="rId73"/>
+    <hyperlink ref="H75" r:id="rId74"/>
+    <hyperlink ref="H76" r:id="rId75"/>
+    <hyperlink ref="H77" r:id="rId76"/>
+    <hyperlink ref="H78" r:id="rId77"/>
+    <hyperlink ref="H79" r:id="rId78"/>
+    <hyperlink ref="H80" r:id="rId79"/>
+    <hyperlink ref="H81" r:id="rId80"/>
+    <hyperlink ref="H82" r:id="rId81"/>
+    <hyperlink ref="H83" r:id="rId82"/>
+    <hyperlink ref="H84" r:id="rId83"/>
+    <hyperlink ref="H85" r:id="rId84"/>
+    <hyperlink ref="H86" r:id="rId85"/>
+    <hyperlink ref="H87" r:id="rId86"/>
+    <hyperlink ref="H88" r:id="rId87"/>
+    <hyperlink ref="H89" r:id="rId88"/>
+    <hyperlink ref="H90" r:id="rId89"/>
+    <hyperlink ref="H91" r:id="rId90"/>
+    <hyperlink ref="H92" r:id="rId91"/>
+    <hyperlink ref="H93" r:id="rId92"/>
+    <hyperlink ref="H94" r:id="rId93"/>
+    <hyperlink ref="H95" r:id="rId94"/>
+    <hyperlink ref="H96" r:id="rId95"/>
+    <hyperlink ref="H97" r:id="rId96"/>
+    <hyperlink ref="H98" r:id="rId97"/>
+    <hyperlink ref="H99" r:id="rId98"/>
+    <hyperlink ref="H100" r:id="rId99"/>
+    <hyperlink ref="H101" r:id="rId100"/>
+    <hyperlink ref="H102" r:id="rId101"/>
+    <hyperlink ref="H103" r:id="rId102"/>
+    <hyperlink ref="H104" r:id="rId103"/>
+    <hyperlink ref="H105" r:id="rId104"/>
+    <hyperlink ref="H106" r:id="rId105"/>
+    <hyperlink ref="H107" r:id="rId106"/>
+    <hyperlink ref="H108" r:id="rId107"/>
+    <hyperlink ref="H109" r:id="rId108"/>
+    <hyperlink ref="H110" r:id="rId109"/>
+    <hyperlink ref="H111" r:id="rId110"/>
+    <hyperlink ref="H112" r:id="rId111"/>
+    <hyperlink ref="H113" r:id="rId112"/>
+    <hyperlink ref="H114" r:id="rId113"/>
+    <hyperlink ref="H115" r:id="rId114"/>
+    <hyperlink ref="H116" r:id="rId115"/>
+    <hyperlink ref="H117" r:id="rId116"/>
+    <hyperlink ref="H118" r:id="rId117"/>
+    <hyperlink ref="H119" r:id="rId118"/>
+    <hyperlink ref="H120" r:id="rId119"/>
+    <hyperlink ref="H121" r:id="rId120"/>
+    <hyperlink ref="H122" r:id="rId121"/>
+    <hyperlink ref="H123" r:id="rId122"/>
+    <hyperlink ref="H124" r:id="rId123"/>
+    <hyperlink ref="H125" r:id="rId124"/>
+    <hyperlink ref="H126" r:id="rId125"/>
+    <hyperlink ref="H127" r:id="rId126"/>
+    <hyperlink ref="H128" r:id="rId127"/>
+    <hyperlink ref="H129" r:id="rId128"/>
+    <hyperlink ref="H130" r:id="rId129"/>
+    <hyperlink ref="H131" r:id="rId130"/>
+    <hyperlink ref="H132" r:id="rId131"/>
+    <hyperlink ref="H133" r:id="rId132"/>
+    <hyperlink ref="H134" r:id="rId133"/>
+    <hyperlink ref="H135" r:id="rId134"/>
+    <hyperlink ref="H136" r:id="rId135"/>
+    <hyperlink ref="H137" r:id="rId136"/>
+    <hyperlink ref="H138" r:id="rId137"/>
+    <hyperlink ref="H139" r:id="rId138"/>
+    <hyperlink ref="H140" r:id="rId139"/>
+    <hyperlink ref="H141" r:id="rId140"/>
+    <hyperlink ref="H142" r:id="rId141"/>
+    <hyperlink ref="H143" r:id="rId142"/>
+    <hyperlink ref="H144" r:id="rId143"/>
+    <hyperlink ref="H145" r:id="rId144"/>
+    <hyperlink ref="H146" r:id="rId145"/>
+    <hyperlink ref="H147" r:id="rId146"/>
+    <hyperlink ref="H148" r:id="rId147"/>
+    <hyperlink ref="H149" r:id="rId148"/>
+    <hyperlink ref="H150" r:id="rId149"/>
+    <hyperlink ref="H151" r:id="rId150"/>
+    <hyperlink ref="H152" r:id="rId151"/>
+    <hyperlink ref="H153" r:id="rId152"/>
+    <hyperlink ref="H154" r:id="rId153"/>
+    <hyperlink ref="H155" r:id="rId154"/>
+    <hyperlink ref="H156" r:id="rId155"/>
+    <hyperlink ref="H157" r:id="rId156"/>
+    <hyperlink ref="H158" r:id="rId157"/>
+    <hyperlink ref="H159" r:id="rId158"/>
+    <hyperlink ref="H160" r:id="rId159"/>
+    <hyperlink ref="H161" r:id="rId160"/>
+    <hyperlink ref="H162" r:id="rId161"/>
+    <hyperlink ref="H163" r:id="rId162"/>
+    <hyperlink ref="H164" r:id="rId163"/>
+    <hyperlink ref="H165" r:id="rId164"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/docs/xlsx/jobs-2026-08-19.xlsx
+++ b/docs/xlsx/jobs-2026-08-19.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1341" uniqueCount="876">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1418" uniqueCount="910">
   <si>
     <t>Title</t>
   </si>
@@ -1516,6 +1516,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/1ed4a112387e42248c48aba0d52aa9a8-grants-officer-safety-net-new-york</t>
   </si>
   <si>
+    <t>Head of Education - Inclusive Education, Mumbai</t>
+  </si>
+  <si>
+    <t>Ground Zero</t>
+  </si>
+  <si>
+    <t>Mumbai, Mumbai, IN</t>
+  </si>
+  <si>
+    <t>INR 2000000.00 - 2500000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/611a759d267647aa88d0b01163b528ba-head-of-education-inclusive-education-mumbai-ground-zero-mumbai</t>
+  </si>
+  <si>
     <t>Head of School (Director)</t>
   </si>
   <si>
@@ -1675,6 +1693,33 @@
     <t>https://www.idealist.org/en/job/418f9c2aa0e7494aa2ff081d74d05e60-major-gifts-officer-national-fundraising-capital-campaign-meridian-international-center-washington</t>
   </si>
   <si>
+    <t>Meridian International</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/418f9c2aa0e7494aa2ff081d74d05e60-major-gifts-officer-national-fundraising-capital-campaign-meridian-international-washington</t>
+  </si>
+  <si>
+    <t>Manager - Government Partnerships, Ahmedabad</t>
+  </si>
+  <si>
+    <t>Ahemdabad, Ahemdabad, IN</t>
+  </si>
+  <si>
+    <t>INR 1000000.00 - 1500000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/091b4fc5c69f4d93b7a6c97c79d0870e-manager-government-partnerships-ahmedabad-ground-zero-ahemdabad</t>
+  </si>
+  <si>
+    <t>Manager - Policy Engagement, Mumbai</t>
+  </si>
+  <si>
+    <t>INR 1500000.00 - 2000000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b23860d1f419421788f5846b3854107f-manager-policy-engagement-mumbai-ground-zero-mumbai</t>
+  </si>
+  <si>
     <t>Manager of Development</t>
   </si>
   <si>
@@ -1774,6 +1819,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/80e1e4d4507f4cc09fb5afbae25aeddd-marketing-associate-rebuilding-together-washington</t>
   </si>
   <si>
+    <t>Media and Communications Officer</t>
+  </si>
+  <si>
+    <t>SEED Madagascar</t>
+  </si>
+  <si>
+    <t>Taolagnaro, Anosy, MG</t>
+  </si>
+  <si>
+    <t>MGA 1800000.00 - 1800000.00/month</t>
+  </si>
+  <si>
+    <t>Community Development, Economic Development, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a8b54d6aebed4af58d5ae0df472c8d75-media-and-communications-officer-seed-madagascar-taolagnaro</t>
+  </si>
+  <si>
     <t>Mental Wellness Therapist</t>
   </si>
   <si>
@@ -1936,6 +1999,12 @@
     <t>https://www.idealist.org/en/nonprofit-job/0b1e4b64f5974488997cf279878504fd-operations-director-manager-irreplaceable-new-york</t>
   </si>
   <si>
+    <t>New Advocacy Organization for AI Regulation</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0b1e4b64f5974488997cf279878504fd-operations-director-manager-new-advocacy-organization-for-ai-regulation-new-york</t>
+  </si>
+  <si>
     <t>Operations Manager</t>
   </si>
   <si>
@@ -1975,6 +2044,9 @@
     <t>https://www.idealist.org/en/nonprofit-job/4a404ad726ed419694db826c59473afa-organizing-director-irreplaceable-new-york</t>
   </si>
   <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4a404ad726ed419694db826c59473afa-organizing-director-new-advocacy-organization-for-ai-regulation-new-york</t>
+  </si>
+  <si>
     <t>Paralegal</t>
   </si>
   <si>
@@ -2158,6 +2230,12 @@
     <t>https://www.idealist.org/en/nonprofit-job/acdb85e42be64ee4a8af64e2a7cb5776-program-specialist-boston-30hrsweek-hybrid-literations-boston</t>
   </si>
   <si>
+    <t>Programme Officer - Sustainable Agriculture and Rural Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2d33c485b9ef4858bf6cfb75b011fb61-programme-officer-sustainable-agriculture-and-rural-development-seed-madagascar-taolagnaro</t>
+  </si>
+  <si>
     <t>Programs Coordinator</t>
   </si>
   <si>
@@ -2251,6 +2329,15 @@
     <t>https://www.idealist.org/en/nonprofit-job/bdf0e83fa7d249cf91f90091278be48f-senior-accountant-roseland</t>
   </si>
   <si>
+    <t>Senior Conservation Research Assistant (Madagascar)</t>
+  </si>
+  <si>
+    <t>Environment, Community Development, Climate Change</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ea6a68a7670143c384f9e0a998a893b3-senior-conservation-research-assistant-madagascar-seed-madagascar-taolagnaro</t>
+  </si>
+  <si>
     <t>Senior Consultant (Grant Writer, Foundation Relations, Institutional Giving)</t>
   </si>
   <si>
@@ -2272,6 +2359,9 @@
     <t>https://www.idealist.org/en/nonprofit-job/28b77aeed83b48e2ad2080ad19979cac-senior-digital-manager-irreplaceable-new-york</t>
   </si>
   <si>
+    <t>https://www.idealist.org/en/nonprofit-job/28b77aeed83b48e2ad2080ad19979cac-senior-digital-manager-new-advocacy-organization-for-ai-regulation-new-york</t>
+  </si>
+  <si>
     <t>Senior Digital Strategy &amp; Engagement Associate (part-time)</t>
   </si>
   <si>
@@ -2345,6 +2435,18 @@
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/35282756331842148711d85d585f9cbe-senior-health-care-policy-analyst-the-commonwealth-institute-for-fiscal-analysis-richmond</t>
+  </si>
+  <si>
+    <t>Senior Manager - Fundraising, Pune</t>
+  </si>
+  <si>
+    <t>Pune, Pune, IN</t>
+  </si>
+  <si>
+    <t>INR 2000000.00 - 2200000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e51919bd815c4953b303f28c891b8548-senior-manager-fundraising-pune-ground-zero-pune</t>
   </si>
   <si>
     <t>Senior Manager, Human Resources</t>
@@ -3679,7 +3781,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H165"/>
+  <dimension ref="A1:H176"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -5480,30 +5582,30 @@
         <v>144</v>
       </c>
       <c r="E78" t="s">
-        <v>138</v>
+        <v>503</v>
       </c>
       <c r="F78" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B79" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C79" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="D79" t="s">
         <v>144</v>
       </c>
       <c r="E79" t="s">
-        <v>508</v>
+        <v>138</v>
       </c>
       <c r="F79" t="s">
         <v>509</v>
@@ -5526,251 +5628,251 @@
         <v>144</v>
       </c>
       <c r="E80" t="s">
-        <v>138</v>
+        <v>514</v>
       </c>
       <c r="F80" t="s">
-        <v>443</v>
+        <v>515</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="B81" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="C81" t="s">
-        <v>155</v>
+        <v>519</v>
       </c>
       <c r="D81" t="s">
         <v>144</v>
       </c>
       <c r="E81" t="s">
-        <v>517</v>
+        <v>138</v>
       </c>
       <c r="F81" t="s">
         <v>443</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="B82" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="C82" t="s">
-        <v>173</v>
+        <v>155</v>
       </c>
       <c r="D82" t="s">
         <v>144</v>
       </c>
       <c r="E82" t="s">
-        <v>447</v>
+        <v>523</v>
       </c>
       <c r="F82" t="s">
-        <v>407</v>
+        <v>443</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="B83" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="C83" t="s">
-        <v>330</v>
+        <v>173</v>
       </c>
       <c r="D83" t="s">
         <v>144</v>
       </c>
       <c r="E83" t="s">
-        <v>524</v>
+        <v>447</v>
       </c>
       <c r="F83" t="s">
-        <v>525</v>
+        <v>407</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B84" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C84" t="s">
-        <v>507</v>
+        <v>330</v>
       </c>
       <c r="D84" t="s">
         <v>144</v>
       </c>
       <c r="E84" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="F84" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B85" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C85" t="s">
-        <v>534</v>
+        <v>513</v>
       </c>
       <c r="D85" t="s">
-        <v>162</v>
+        <v>144</v>
       </c>
       <c r="E85" t="s">
         <v>535</v>
       </c>
       <c r="F85" t="s">
-        <v>138</v>
+        <v>536</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B86" t="s">
-        <v>209</v>
+        <v>539</v>
       </c>
       <c r="C86" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="D86" t="s">
         <v>162</v>
       </c>
       <c r="E86" t="s">
+        <v>541</v>
+      </c>
+      <c r="F86" t="s">
         <v>138</v>
       </c>
-      <c r="F86" t="s">
-        <v>215</v>
-      </c>
       <c r="H86" s="2" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="B87" t="s">
-        <v>541</v>
+        <v>209</v>
       </c>
       <c r="C87" t="s">
-        <v>173</v>
+        <v>544</v>
       </c>
       <c r="D87" t="s">
-        <v>144</v>
+        <v>162</v>
       </c>
       <c r="E87" t="s">
-        <v>542</v>
+        <v>138</v>
       </c>
       <c r="F87" t="s">
-        <v>543</v>
+        <v>215</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B88" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C88" t="s">
-        <v>314</v>
+        <v>173</v>
       </c>
       <c r="D88" t="s">
         <v>144</v>
       </c>
       <c r="E88" t="s">
-        <v>360</v>
+        <v>548</v>
       </c>
       <c r="F88" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="H88" s="2" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="B89" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="C89" t="s">
-        <v>359</v>
+        <v>314</v>
       </c>
       <c r="D89" t="s">
         <v>144</v>
       </c>
       <c r="E89" t="s">
-        <v>551</v>
+        <v>360</v>
       </c>
       <c r="F89" t="s">
-        <v>138</v>
+        <v>553</v>
       </c>
       <c r="H89" s="2" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="B90" t="s">
-        <v>506</v>
+        <v>556</v>
       </c>
       <c r="C90" t="s">
-        <v>507</v>
+        <v>359</v>
       </c>
       <c r="D90" t="s">
         <v>144</v>
       </c>
       <c r="E90" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="F90" t="s">
-        <v>555</v>
+        <v>138</v>
       </c>
       <c r="H90" s="2" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="B91" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C91" t="s">
         <v>359</v>
@@ -5779,7 +5881,7 @@
         <v>144</v>
       </c>
       <c r="E91" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="F91" t="s">
         <v>138</v>
@@ -5793,180 +5895,180 @@
         <v>561</v>
       </c>
       <c r="B92" t="s">
+        <v>501</v>
+      </c>
+      <c r="C92" t="s">
         <v>562</v>
       </c>
-      <c r="C92" t="s">
+      <c r="D92" t="s">
+        <v>144</v>
+      </c>
+      <c r="E92" t="s">
         <v>563</v>
       </c>
-      <c r="D92" t="s">
-        <v>144</v>
-      </c>
-      <c r="E92" t="s">
+      <c r="F92" t="s">
+        <v>504</v>
+      </c>
+      <c r="H92" s="2" t="s">
         <v>564</v>
-      </c>
-      <c r="F92" t="s">
-        <v>565</v>
-      </c>
-      <c r="H92" s="2" t="s">
-        <v>566</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
+        <v>565</v>
+      </c>
+      <c r="B93" t="s">
+        <v>501</v>
+      </c>
+      <c r="C93" t="s">
+        <v>502</v>
+      </c>
+      <c r="D93" t="s">
+        <v>144</v>
+      </c>
+      <c r="E93" t="s">
+        <v>566</v>
+      </c>
+      <c r="F93" t="s">
+        <v>504</v>
+      </c>
+      <c r="H93" s="2" t="s">
         <v>567</v>
-      </c>
-      <c r="B93" t="s">
-        <v>568</v>
-      </c>
-      <c r="C93" t="s">
-        <v>569</v>
-      </c>
-      <c r="D93" t="s">
-        <v>144</v>
-      </c>
-      <c r="E93" t="s">
-        <v>570</v>
-      </c>
-      <c r="F93" t="s">
-        <v>571</v>
-      </c>
-      <c r="H93" s="2" t="s">
-        <v>572</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>573</v>
+        <v>568</v>
       </c>
       <c r="B94" t="s">
-        <v>528</v>
+        <v>512</v>
       </c>
       <c r="C94" t="s">
-        <v>507</v>
+        <v>513</v>
       </c>
       <c r="D94" t="s">
         <v>144</v>
       </c>
       <c r="E94" t="s">
-        <v>574</v>
+        <v>569</v>
       </c>
       <c r="F94" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="H94" s="2" t="s">
-        <v>576</v>
+        <v>571</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>577</v>
+        <v>572</v>
       </c>
       <c r="B95" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="C95" t="s">
-        <v>155</v>
+        <v>359</v>
       </c>
       <c r="D95" t="s">
         <v>144</v>
       </c>
       <c r="E95" t="s">
-        <v>579</v>
+        <v>574</v>
       </c>
       <c r="F95" t="s">
-        <v>433</v>
+        <v>138</v>
       </c>
       <c r="H95" s="2" t="s">
-        <v>580</v>
+        <v>575</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
+        <v>576</v>
+      </c>
+      <c r="B96" t="s">
+        <v>577</v>
+      </c>
+      <c r="C96" t="s">
+        <v>578</v>
+      </c>
+      <c r="D96" t="s">
+        <v>144</v>
+      </c>
+      <c r="E96" t="s">
+        <v>579</v>
+      </c>
+      <c r="F96" t="s">
+        <v>580</v>
+      </c>
+      <c r="H96" s="2" t="s">
         <v>581</v>
-      </c>
-      <c r="B96" t="s">
-        <v>582</v>
-      </c>
-      <c r="C96" t="s">
-        <v>247</v>
-      </c>
-      <c r="D96" t="s">
-        <v>144</v>
-      </c>
-      <c r="E96" t="s">
-        <v>583</v>
-      </c>
-      <c r="F96" t="s">
-        <v>584</v>
-      </c>
-      <c r="H96" s="2" t="s">
-        <v>585</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
+        <v>582</v>
+      </c>
+      <c r="B97" t="s">
+        <v>583</v>
+      </c>
+      <c r="C97" t="s">
+        <v>584</v>
+      </c>
+      <c r="D97" t="s">
+        <v>144</v>
+      </c>
+      <c r="E97" t="s">
+        <v>585</v>
+      </c>
+      <c r="F97" t="s">
         <v>586</v>
       </c>
-      <c r="B97" t="s">
+      <c r="H97" s="2" t="s">
         <v>587</v>
-      </c>
-      <c r="C97" t="s">
-        <v>330</v>
-      </c>
-      <c r="D97" t="s">
-        <v>144</v>
-      </c>
-      <c r="E97" t="s">
-        <v>588</v>
-      </c>
-      <c r="F97" t="s">
-        <v>589</v>
-      </c>
-      <c r="H97" s="2" t="s">
-        <v>590</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
+        <v>588</v>
+      </c>
+      <c r="B98" t="s">
+        <v>534</v>
+      </c>
+      <c r="C98" t="s">
+        <v>513</v>
+      </c>
+      <c r="D98" t="s">
+        <v>144</v>
+      </c>
+      <c r="E98" t="s">
+        <v>589</v>
+      </c>
+      <c r="F98" t="s">
+        <v>590</v>
+      </c>
+      <c r="H98" s="2" t="s">
         <v>591</v>
-      </c>
-      <c r="B98" t="s">
-        <v>441</v>
-      </c>
-      <c r="C98" t="s">
-        <v>155</v>
-      </c>
-      <c r="D98" t="s">
-        <v>144</v>
-      </c>
-      <c r="E98" t="s">
-        <v>554</v>
-      </c>
-      <c r="F98" t="s">
-        <v>443</v>
-      </c>
-      <c r="H98" s="2" t="s">
-        <v>592</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
+        <v>592</v>
+      </c>
+      <c r="B99" t="s">
         <v>593</v>
       </c>
-      <c r="B99" t="s">
+      <c r="C99" t="s">
+        <v>155</v>
+      </c>
+      <c r="D99" t="s">
+        <v>144</v>
+      </c>
+      <c r="E99" t="s">
         <v>594</v>
       </c>
-      <c r="C99" t="s">
-        <v>472</v>
-      </c>
-      <c r="D99" t="s">
-        <v>144</v>
-      </c>
-      <c r="E99" t="s">
-        <v>156</v>
-      </c>
       <c r="F99" t="s">
-        <v>138</v>
+        <v>433</v>
       </c>
       <c r="H99" s="2" t="s">
         <v>595</v>
@@ -5980,36 +6082,36 @@
         <v>597</v>
       </c>
       <c r="C100" t="s">
+        <v>247</v>
+      </c>
+      <c r="D100" t="s">
+        <v>144</v>
+      </c>
+      <c r="E100" t="s">
         <v>598</v>
       </c>
-      <c r="D100" t="s">
-        <v>144</v>
-      </c>
-      <c r="E100" t="s">
+      <c r="F100" t="s">
         <v>599</v>
       </c>
-      <c r="F100" t="s">
+      <c r="H100" s="2" t="s">
         <v>600</v>
-      </c>
-      <c r="H100" s="2" t="s">
-        <v>601</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
+        <v>601</v>
+      </c>
+      <c r="B101" t="s">
         <v>602</v>
       </c>
-      <c r="B101" t="s">
+      <c r="C101" t="s">
         <v>603</v>
       </c>
-      <c r="C101" t="s">
+      <c r="D101" t="s">
+        <v>144</v>
+      </c>
+      <c r="E101" t="s">
         <v>604</v>
-      </c>
-      <c r="D101" t="s">
-        <v>144</v>
-      </c>
-      <c r="E101" t="s">
-        <v>315</v>
       </c>
       <c r="F101" t="s">
         <v>605</v>
@@ -6026,648 +6128,648 @@
         <v>608</v>
       </c>
       <c r="C102" t="s">
+        <v>330</v>
+      </c>
+      <c r="D102" t="s">
+        <v>144</v>
+      </c>
+      <c r="E102" t="s">
         <v>609</v>
       </c>
-      <c r="D102" t="s">
-        <v>144</v>
-      </c>
-      <c r="E102" t="s">
+      <c r="F102" t="s">
         <v>610</v>
       </c>
-      <c r="F102" t="s">
+      <c r="H102" s="2" t="s">
         <v>611</v>
-      </c>
-      <c r="H102" s="2" t="s">
-        <v>612</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
+        <v>612</v>
+      </c>
+      <c r="B103" t="s">
+        <v>441</v>
+      </c>
+      <c r="C103" t="s">
+        <v>155</v>
+      </c>
+      <c r="D103" t="s">
+        <v>144</v>
+      </c>
+      <c r="E103" t="s">
+        <v>569</v>
+      </c>
+      <c r="F103" t="s">
+        <v>443</v>
+      </c>
+      <c r="H103" s="2" t="s">
         <v>613</v>
-      </c>
-      <c r="B103" t="s">
-        <v>614</v>
-      </c>
-      <c r="C103" t="s">
-        <v>173</v>
-      </c>
-      <c r="D103" t="s">
-        <v>144</v>
-      </c>
-      <c r="E103" t="s">
-        <v>615</v>
-      </c>
-      <c r="F103" t="s">
-        <v>138</v>
-      </c>
-      <c r="H103" s="2" t="s">
-        <v>616</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="B104" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="C104" t="s">
-        <v>619</v>
+        <v>472</v>
       </c>
       <c r="D104" t="s">
-        <v>202</v>
+        <v>144</v>
       </c>
       <c r="E104" t="s">
-        <v>203</v>
+        <v>156</v>
       </c>
       <c r="F104" t="s">
-        <v>620</v>
+        <v>138</v>
       </c>
       <c r="H104" s="2" t="s">
-        <v>621</v>
+        <v>616</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
+        <v>617</v>
+      </c>
+      <c r="B105" t="s">
+        <v>618</v>
+      </c>
+      <c r="C105" t="s">
+        <v>619</v>
+      </c>
+      <c r="D105" t="s">
+        <v>144</v>
+      </c>
+      <c r="E105" t="s">
+        <v>620</v>
+      </c>
+      <c r="F105" t="s">
+        <v>621</v>
+      </c>
+      <c r="H105" s="2" t="s">
         <v>622</v>
-      </c>
-      <c r="B105" t="s">
-        <v>623</v>
-      </c>
-      <c r="C105" t="s">
-        <v>624</v>
-      </c>
-      <c r="D105" t="s">
-        <v>162</v>
-      </c>
-      <c r="E105" t="s">
-        <v>625</v>
-      </c>
-      <c r="F105" t="s">
-        <v>626</v>
-      </c>
-      <c r="H105" s="2" t="s">
-        <v>627</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>628</v>
+        <v>623</v>
       </c>
       <c r="B106" t="s">
-        <v>292</v>
+        <v>624</v>
       </c>
       <c r="C106" t="s">
-        <v>293</v>
+        <v>625</v>
       </c>
       <c r="D106" t="s">
-        <v>162</v>
+        <v>144</v>
       </c>
       <c r="E106" t="s">
-        <v>629</v>
+        <v>315</v>
       </c>
       <c r="F106" t="s">
-        <v>295</v>
+        <v>626</v>
       </c>
       <c r="H106" s="2" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
+        <v>628</v>
+      </c>
+      <c r="B107" t="s">
+        <v>629</v>
+      </c>
+      <c r="C107" t="s">
+        <v>630</v>
+      </c>
+      <c r="D107" t="s">
+        <v>144</v>
+      </c>
+      <c r="E107" t="s">
         <v>631</v>
       </c>
-      <c r="B107" t="s">
+      <c r="F107" t="s">
         <v>632</v>
       </c>
-      <c r="C107" t="s">
-        <v>299</v>
-      </c>
-      <c r="D107" t="s">
-        <v>144</v>
-      </c>
-      <c r="E107" t="s">
+      <c r="H107" s="2" t="s">
         <v>633</v>
-      </c>
-      <c r="F107" t="s">
-        <v>138</v>
-      </c>
-      <c r="H107" s="2" t="s">
-        <v>634</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
+        <v>634</v>
+      </c>
+      <c r="B108" t="s">
         <v>635</v>
       </c>
-      <c r="B108" t="s">
+      <c r="C108" t="s">
+        <v>173</v>
+      </c>
+      <c r="D108" t="s">
+        <v>144</v>
+      </c>
+      <c r="E108" t="s">
         <v>636</v>
       </c>
-      <c r="C108" t="s">
-        <v>247</v>
-      </c>
-      <c r="D108" t="s">
-        <v>144</v>
-      </c>
-      <c r="E108" t="s">
+      <c r="F108" t="s">
+        <v>138</v>
+      </c>
+      <c r="H108" s="2" t="s">
         <v>637</v>
-      </c>
-      <c r="F108" t="s">
-        <v>638</v>
-      </c>
-      <c r="H108" s="2" t="s">
-        <v>639</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
+        <v>638</v>
+      </c>
+      <c r="B109" t="s">
+        <v>639</v>
+      </c>
+      <c r="C109" t="s">
         <v>640</v>
       </c>
-      <c r="B109" t="s">
+      <c r="D109" t="s">
+        <v>202</v>
+      </c>
+      <c r="E109" t="s">
+        <v>203</v>
+      </c>
+      <c r="F109" t="s">
         <v>641</v>
       </c>
-      <c r="C109" t="s">
-        <v>258</v>
-      </c>
-      <c r="D109" t="s">
-        <v>144</v>
-      </c>
-      <c r="E109" t="s">
+      <c r="H109" s="2" t="s">
         <v>642</v>
-      </c>
-      <c r="F109" t="s">
-        <v>643</v>
-      </c>
-      <c r="H109" s="2" t="s">
-        <v>644</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
+        <v>643</v>
+      </c>
+      <c r="B110" t="s">
+        <v>644</v>
+      </c>
+      <c r="C110" t="s">
         <v>645</v>
       </c>
-      <c r="B110" t="s">
+      <c r="D110" t="s">
+        <v>162</v>
+      </c>
+      <c r="E110" t="s">
         <v>646</v>
       </c>
-      <c r="C110" t="s">
-        <v>155</v>
-      </c>
-      <c r="D110" t="s">
-        <v>144</v>
-      </c>
-      <c r="E110" t="s">
+      <c r="F110" t="s">
         <v>647</v>
       </c>
-      <c r="F110" t="s">
+      <c r="H110" s="2" t="s">
         <v>648</v>
-      </c>
-      <c r="H110" s="2" t="s">
-        <v>649</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
+        <v>649</v>
+      </c>
+      <c r="B111" t="s">
+        <v>292</v>
+      </c>
+      <c r="C111" t="s">
+        <v>293</v>
+      </c>
+      <c r="D111" t="s">
+        <v>162</v>
+      </c>
+      <c r="E111" t="s">
         <v>650</v>
       </c>
-      <c r="B111" t="s">
-        <v>636</v>
-      </c>
-      <c r="C111" t="s">
-        <v>247</v>
-      </c>
-      <c r="D111" t="s">
-        <v>144</v>
-      </c>
-      <c r="E111" t="s">
+      <c r="F111" t="s">
+        <v>295</v>
+      </c>
+      <c r="H111" s="2" t="s">
         <v>651</v>
-      </c>
-      <c r="F111" t="s">
-        <v>638</v>
-      </c>
-      <c r="H111" s="2" t="s">
-        <v>652</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
+        <v>652</v>
+      </c>
+      <c r="B112" t="s">
         <v>653</v>
       </c>
-      <c r="B112" t="s">
+      <c r="C112" t="s">
+        <v>299</v>
+      </c>
+      <c r="D112" t="s">
+        <v>144</v>
+      </c>
+      <c r="E112" t="s">
         <v>654</v>
       </c>
-      <c r="C112" t="s">
-        <v>155</v>
-      </c>
-      <c r="D112" t="s">
-        <v>144</v>
-      </c>
-      <c r="E112" t="s">
+      <c r="F112" t="s">
+        <v>138</v>
+      </c>
+      <c r="H112" s="2" t="s">
         <v>655</v>
-      </c>
-      <c r="F112" t="s">
-        <v>185</v>
-      </c>
-      <c r="H112" s="2" t="s">
-        <v>656</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
+        <v>656</v>
+      </c>
+      <c r="B113" t="s">
         <v>657</v>
       </c>
-      <c r="B113" t="s">
+      <c r="C113" t="s">
+        <v>247</v>
+      </c>
+      <c r="D113" t="s">
+        <v>144</v>
+      </c>
+      <c r="E113" t="s">
         <v>658</v>
       </c>
-      <c r="C113" t="s">
-        <v>219</v>
-      </c>
-      <c r="D113" t="s">
-        <v>162</v>
-      </c>
-      <c r="E113" t="s">
+      <c r="F113" t="s">
         <v>659</v>
       </c>
-      <c r="F113" t="s">
+      <c r="H113" s="2" t="s">
         <v>660</v>
-      </c>
-      <c r="H113" s="2" t="s">
-        <v>661</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
+        <v>656</v>
+      </c>
+      <c r="B114" t="s">
+        <v>661</v>
+      </c>
+      <c r="C114" t="s">
+        <v>247</v>
+      </c>
+      <c r="D114" t="s">
+        <v>144</v>
+      </c>
+      <c r="E114" t="s">
+        <v>658</v>
+      </c>
+      <c r="F114" t="s">
+        <v>659</v>
+      </c>
+      <c r="H114" s="2" t="s">
         <v>662</v>
-      </c>
-      <c r="B114" t="s">
-        <v>663</v>
-      </c>
-      <c r="C114" t="s">
-        <v>664</v>
-      </c>
-      <c r="D114" t="s">
-        <v>144</v>
-      </c>
-      <c r="E114" t="s">
-        <v>138</v>
-      </c>
-      <c r="F114" t="s">
-        <v>138</v>
-      </c>
-      <c r="H114" s="2" t="s">
-        <v>665</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
+        <v>663</v>
+      </c>
+      <c r="B115" t="s">
+        <v>664</v>
+      </c>
+      <c r="C115" t="s">
+        <v>258</v>
+      </c>
+      <c r="D115" t="s">
+        <v>144</v>
+      </c>
+      <c r="E115" t="s">
+        <v>665</v>
+      </c>
+      <c r="F115" t="s">
         <v>666</v>
       </c>
-      <c r="B115" t="s">
+      <c r="H115" s="2" t="s">
         <v>667</v>
-      </c>
-      <c r="C115" t="s">
-        <v>299</v>
-      </c>
-      <c r="D115" t="s">
-        <v>162</v>
-      </c>
-      <c r="E115" t="s">
-        <v>668</v>
-      </c>
-      <c r="F115" t="s">
-        <v>669</v>
-      </c>
-      <c r="H115" s="2" t="s">
-        <v>670</v>
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
+        <v>668</v>
+      </c>
+      <c r="B116" t="s">
+        <v>669</v>
+      </c>
+      <c r="C116" t="s">
+        <v>155</v>
+      </c>
+      <c r="D116" t="s">
+        <v>144</v>
+      </c>
+      <c r="E116" t="s">
+        <v>670</v>
+      </c>
+      <c r="F116" t="s">
         <v>671</v>
       </c>
-      <c r="B116" t="s">
+      <c r="H116" s="2" t="s">
         <v>672</v>
-      </c>
-      <c r="C116" t="s">
-        <v>247</v>
-      </c>
-      <c r="D116" t="s">
-        <v>168</v>
-      </c>
-      <c r="E116" t="s">
-        <v>673</v>
-      </c>
-      <c r="F116" t="s">
-        <v>674</v>
-      </c>
-      <c r="H116" s="2" t="s">
-        <v>675</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="B117" t="s">
-        <v>481</v>
+        <v>657</v>
       </c>
       <c r="C117" t="s">
-        <v>482</v>
+        <v>247</v>
       </c>
       <c r="D117" t="s">
         <v>144</v>
       </c>
       <c r="E117" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
       <c r="F117" t="s">
-        <v>484</v>
+        <v>659</v>
       </c>
       <c r="H117" s="2" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>679</v>
+        <v>673</v>
       </c>
       <c r="B118" t="s">
-        <v>680</v>
+        <v>661</v>
       </c>
       <c r="C118" t="s">
-        <v>330</v>
+        <v>247</v>
       </c>
       <c r="D118" t="s">
-        <v>162</v>
+        <v>144</v>
       </c>
       <c r="E118" t="s">
-        <v>138</v>
+        <v>674</v>
       </c>
       <c r="F118" t="s">
-        <v>138</v>
+        <v>659</v>
       </c>
       <c r="H118" s="2" t="s">
-        <v>681</v>
+        <v>676</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>682</v>
+        <v>677</v>
       </c>
       <c r="B119" t="s">
-        <v>683</v>
+        <v>678</v>
       </c>
       <c r="C119" t="s">
-        <v>684</v>
+        <v>155</v>
       </c>
       <c r="D119" t="s">
         <v>144</v>
       </c>
       <c r="E119" t="s">
-        <v>685</v>
+        <v>679</v>
       </c>
       <c r="F119" t="s">
-        <v>281</v>
+        <v>185</v>
       </c>
       <c r="H119" s="2" t="s">
-        <v>686</v>
+        <v>680</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>687</v>
+        <v>681</v>
       </c>
       <c r="B120" t="s">
-        <v>209</v>
+        <v>682</v>
       </c>
       <c r="C120" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="D120" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="E120" t="s">
-        <v>138</v>
+        <v>683</v>
       </c>
       <c r="F120" t="s">
-        <v>285</v>
+        <v>684</v>
       </c>
       <c r="H120" s="2" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
+        <v>686</v>
+      </c>
+      <c r="B121" t="s">
+        <v>687</v>
+      </c>
+      <c r="C121" t="s">
+        <v>688</v>
+      </c>
+      <c r="D121" t="s">
+        <v>144</v>
+      </c>
+      <c r="E121" t="s">
+        <v>138</v>
+      </c>
+      <c r="F121" t="s">
+        <v>138</v>
+      </c>
+      <c r="H121" s="2" t="s">
         <v>689</v>
-      </c>
-      <c r="B121" t="s">
-        <v>690</v>
-      </c>
-      <c r="C121" t="s">
-        <v>691</v>
-      </c>
-      <c r="D121" t="s">
-        <v>144</v>
-      </c>
-      <c r="E121" t="s">
-        <v>692</v>
-      </c>
-      <c r="F121" t="s">
-        <v>693</v>
-      </c>
-      <c r="H121" s="2" t="s">
-        <v>694</v>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>695</v>
+        <v>690</v>
       </c>
       <c r="B122" t="s">
-        <v>696</v>
+        <v>691</v>
       </c>
       <c r="C122" t="s">
-        <v>697</v>
+        <v>299</v>
       </c>
       <c r="D122" t="s">
-        <v>144</v>
+        <v>162</v>
       </c>
       <c r="E122" t="s">
-        <v>698</v>
+        <v>692</v>
       </c>
       <c r="F122" t="s">
-        <v>699</v>
+        <v>693</v>
       </c>
       <c r="H122" s="2" t="s">
-        <v>700</v>
+        <v>694</v>
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>701</v>
+        <v>695</v>
       </c>
       <c r="B123" t="s">
-        <v>702</v>
+        <v>696</v>
       </c>
       <c r="C123" t="s">
-        <v>359</v>
+        <v>247</v>
       </c>
       <c r="D123" t="s">
-        <v>144</v>
+        <v>168</v>
       </c>
       <c r="E123" t="s">
-        <v>703</v>
+        <v>697</v>
       </c>
       <c r="F123" t="s">
-        <v>704</v>
+        <v>698</v>
       </c>
       <c r="H123" s="2" t="s">
-        <v>705</v>
+        <v>699</v>
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>706</v>
+        <v>700</v>
       </c>
       <c r="B124" t="s">
-        <v>696</v>
+        <v>481</v>
       </c>
       <c r="C124" t="s">
-        <v>707</v>
+        <v>482</v>
       </c>
       <c r="D124" t="s">
         <v>144</v>
       </c>
       <c r="E124" t="s">
-        <v>554</v>
+        <v>701</v>
       </c>
       <c r="F124" t="s">
-        <v>699</v>
+        <v>484</v>
       </c>
       <c r="H124" s="2" t="s">
-        <v>708</v>
+        <v>702</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>709</v>
+        <v>703</v>
       </c>
       <c r="B125" t="s">
-        <v>710</v>
+        <v>704</v>
       </c>
       <c r="C125" t="s">
-        <v>472</v>
+        <v>330</v>
       </c>
       <c r="D125" t="s">
         <v>162</v>
       </c>
       <c r="E125" t="s">
-        <v>711</v>
+        <v>138</v>
       </c>
       <c r="F125" t="s">
-        <v>712</v>
+        <v>138</v>
       </c>
       <c r="H125" s="2" t="s">
-        <v>713</v>
+        <v>705</v>
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>714</v>
+        <v>706</v>
       </c>
       <c r="B126" t="s">
-        <v>715</v>
+        <v>707</v>
       </c>
       <c r="C126" t="s">
-        <v>299</v>
+        <v>708</v>
       </c>
       <c r="D126" t="s">
         <v>144</v>
       </c>
       <c r="E126" t="s">
-        <v>716</v>
+        <v>709</v>
       </c>
       <c r="F126" t="s">
-        <v>717</v>
+        <v>281</v>
       </c>
       <c r="H126" s="2" t="s">
-        <v>718</v>
+        <v>710</v>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>719</v>
+        <v>711</v>
       </c>
       <c r="B127" t="s">
-        <v>720</v>
+        <v>209</v>
       </c>
       <c r="C127" t="s">
-        <v>299</v>
+        <v>214</v>
       </c>
       <c r="D127" t="s">
-        <v>144</v>
+        <v>168</v>
       </c>
       <c r="E127" t="s">
-        <v>721</v>
+        <v>138</v>
       </c>
       <c r="F127" t="s">
-        <v>722</v>
+        <v>285</v>
       </c>
       <c r="H127" s="2" t="s">
-        <v>723</v>
+        <v>712</v>
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>724</v>
+        <v>713</v>
       </c>
       <c r="B128" t="s">
-        <v>725</v>
+        <v>714</v>
       </c>
       <c r="C128" t="s">
-        <v>726</v>
+        <v>715</v>
       </c>
       <c r="D128" t="s">
         <v>144</v>
       </c>
       <c r="E128" t="s">
-        <v>642</v>
+        <v>716</v>
       </c>
       <c r="F128" t="s">
-        <v>727</v>
+        <v>717</v>
       </c>
       <c r="H128" s="2" t="s">
-        <v>728</v>
+        <v>718</v>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>729</v>
+        <v>719</v>
       </c>
       <c r="B129" t="s">
-        <v>730</v>
+        <v>720</v>
       </c>
       <c r="C129" t="s">
-        <v>359</v>
+        <v>721</v>
       </c>
       <c r="D129" t="s">
         <v>144</v>
       </c>
       <c r="E129" t="s">
-        <v>731</v>
+        <v>722</v>
       </c>
       <c r="F129" t="s">
-        <v>138</v>
+        <v>723</v>
       </c>
       <c r="H129" s="2" t="s">
-        <v>732</v>
+        <v>724</v>
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>733</v>
+        <v>725</v>
       </c>
       <c r="B130" t="s">
-        <v>730</v>
+        <v>726</v>
       </c>
       <c r="C130" t="s">
         <v>359</v>
@@ -6676,297 +6778,297 @@
         <v>144</v>
       </c>
       <c r="E130" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="F130" t="s">
-        <v>138</v>
+        <v>728</v>
       </c>
       <c r="H130" s="2" t="s">
-        <v>734</v>
+        <v>729</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>735</v>
+        <v>730</v>
       </c>
       <c r="B131" t="s">
-        <v>736</v>
+        <v>720</v>
       </c>
       <c r="C131" t="s">
-        <v>737</v>
+        <v>731</v>
       </c>
       <c r="D131" t="s">
         <v>144</v>
       </c>
       <c r="E131" t="s">
-        <v>738</v>
+        <v>569</v>
       </c>
       <c r="F131" t="s">
-        <v>407</v>
+        <v>723</v>
       </c>
       <c r="H131" s="2" t="s">
-        <v>739</v>
+        <v>732</v>
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>740</v>
+        <v>733</v>
       </c>
       <c r="B132" t="s">
-        <v>138</v>
+        <v>734</v>
       </c>
       <c r="C132" t="s">
-        <v>741</v>
+        <v>472</v>
       </c>
       <c r="D132" t="s">
-        <v>144</v>
+        <v>162</v>
       </c>
       <c r="E132" t="s">
-        <v>742</v>
+        <v>735</v>
       </c>
       <c r="F132" t="s">
-        <v>743</v>
+        <v>736</v>
       </c>
       <c r="H132" s="2" t="s">
-        <v>744</v>
+        <v>737</v>
       </c>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>745</v>
+        <v>738</v>
       </c>
       <c r="B133" t="s">
-        <v>746</v>
+        <v>602</v>
       </c>
       <c r="C133" t="s">
-        <v>247</v>
+        <v>603</v>
       </c>
       <c r="D133" t="s">
         <v>144</v>
       </c>
       <c r="E133" t="s">
-        <v>747</v>
+        <v>138</v>
       </c>
       <c r="F133" t="s">
-        <v>138</v>
+        <v>605</v>
       </c>
       <c r="H133" s="2" t="s">
-        <v>748</v>
+        <v>739</v>
       </c>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>749</v>
+        <v>740</v>
       </c>
       <c r="B134" t="s">
-        <v>636</v>
+        <v>741</v>
       </c>
       <c r="C134" t="s">
-        <v>247</v>
+        <v>299</v>
       </c>
       <c r="D134" t="s">
         <v>144</v>
       </c>
       <c r="E134" t="s">
-        <v>750</v>
+        <v>742</v>
       </c>
       <c r="F134" t="s">
-        <v>638</v>
+        <v>743</v>
       </c>
       <c r="H134" s="2" t="s">
-        <v>751</v>
+        <v>744</v>
       </c>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>752</v>
+        <v>745</v>
       </c>
       <c r="B135" t="s">
-        <v>142</v>
+        <v>746</v>
       </c>
       <c r="C135" t="s">
-        <v>247</v>
+        <v>299</v>
       </c>
       <c r="D135" t="s">
-        <v>162</v>
+        <v>144</v>
       </c>
       <c r="E135" t="s">
-        <v>753</v>
+        <v>747</v>
       </c>
       <c r="F135" t="s">
-        <v>146</v>
+        <v>748</v>
       </c>
       <c r="H135" s="2" t="s">
-        <v>754</v>
+        <v>749</v>
       </c>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>755</v>
+        <v>750</v>
       </c>
       <c r="B136" t="s">
-        <v>756</v>
+        <v>751</v>
       </c>
       <c r="C136" t="s">
-        <v>757</v>
+        <v>752</v>
       </c>
       <c r="D136" t="s">
         <v>144</v>
       </c>
       <c r="E136" t="s">
-        <v>758</v>
+        <v>665</v>
       </c>
       <c r="F136" t="s">
-        <v>759</v>
+        <v>753</v>
       </c>
       <c r="H136" s="2" t="s">
-        <v>760</v>
+        <v>754</v>
       </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>761</v>
+        <v>755</v>
       </c>
       <c r="B137" t="s">
-        <v>762</v>
+        <v>756</v>
       </c>
       <c r="C137" t="s">
-        <v>173</v>
+        <v>359</v>
       </c>
       <c r="D137" t="s">
         <v>144</v>
       </c>
       <c r="E137" t="s">
-        <v>633</v>
+        <v>757</v>
       </c>
       <c r="F137" t="s">
-        <v>763</v>
+        <v>138</v>
       </c>
       <c r="H137" s="2" t="s">
-        <v>764</v>
+        <v>758</v>
       </c>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>765</v>
+        <v>759</v>
       </c>
       <c r="B138" t="s">
-        <v>766</v>
+        <v>756</v>
       </c>
       <c r="C138" t="s">
-        <v>173</v>
+        <v>359</v>
       </c>
       <c r="D138" t="s">
-        <v>370</v>
+        <v>144</v>
       </c>
       <c r="E138" t="s">
-        <v>767</v>
+        <v>757</v>
       </c>
       <c r="F138" t="s">
         <v>138</v>
       </c>
       <c r="H138" s="2" t="s">
-        <v>768</v>
+        <v>760</v>
       </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>769</v>
+        <v>761</v>
       </c>
       <c r="B139" t="s">
-        <v>770</v>
+        <v>762</v>
       </c>
       <c r="C139" t="s">
-        <v>247</v>
+        <v>763</v>
       </c>
       <c r="D139" t="s">
-        <v>168</v>
+        <v>144</v>
       </c>
       <c r="E139" t="s">
-        <v>771</v>
+        <v>764</v>
       </c>
       <c r="F139" t="s">
-        <v>772</v>
+        <v>407</v>
       </c>
       <c r="H139" s="2" t="s">
-        <v>773</v>
+        <v>765</v>
       </c>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>774</v>
+        <v>766</v>
       </c>
       <c r="B140" t="s">
-        <v>725</v>
+        <v>138</v>
       </c>
       <c r="C140" t="s">
-        <v>726</v>
+        <v>767</v>
       </c>
       <c r="D140" t="s">
         <v>144</v>
       </c>
       <c r="E140" t="s">
-        <v>775</v>
+        <v>768</v>
       </c>
       <c r="F140" t="s">
-        <v>727</v>
+        <v>769</v>
       </c>
       <c r="H140" s="2" t="s">
-        <v>776</v>
+        <v>770</v>
       </c>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>777</v>
+        <v>771</v>
       </c>
       <c r="B141" t="s">
-        <v>778</v>
+        <v>602</v>
       </c>
       <c r="C141" t="s">
-        <v>779</v>
+        <v>603</v>
       </c>
       <c r="D141" t="s">
         <v>144</v>
       </c>
       <c r="E141" t="s">
-        <v>780</v>
+        <v>138</v>
       </c>
       <c r="F141" t="s">
-        <v>781</v>
+        <v>772</v>
       </c>
       <c r="H141" s="2" t="s">
-        <v>782</v>
+        <v>773</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>783</v>
+        <v>774</v>
       </c>
       <c r="B142" t="s">
-        <v>730</v>
+        <v>775</v>
       </c>
       <c r="C142" t="s">
-        <v>359</v>
+        <v>247</v>
       </c>
       <c r="D142" t="s">
         <v>144</v>
       </c>
       <c r="E142" t="s">
-        <v>731</v>
+        <v>776</v>
       </c>
       <c r="F142" t="s">
         <v>138</v>
       </c>
       <c r="H142" s="2" t="s">
-        <v>784</v>
+        <v>777</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>785</v>
+        <v>778</v>
       </c>
       <c r="B143" t="s">
-        <v>268</v>
+        <v>657</v>
       </c>
       <c r="C143" t="s">
         <v>247</v>
@@ -6975,113 +7077,113 @@
         <v>144</v>
       </c>
       <c r="E143" t="s">
-        <v>786</v>
+        <v>779</v>
       </c>
       <c r="F143" t="s">
-        <v>270</v>
+        <v>659</v>
       </c>
       <c r="H143" s="2" t="s">
-        <v>787</v>
+        <v>780</v>
       </c>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>788</v>
+        <v>778</v>
       </c>
       <c r="B144" t="s">
-        <v>789</v>
+        <v>661</v>
       </c>
       <c r="C144" t="s">
-        <v>299</v>
+        <v>247</v>
       </c>
       <c r="D144" t="s">
         <v>144</v>
       </c>
       <c r="E144" t="s">
-        <v>790</v>
+        <v>779</v>
       </c>
       <c r="F144" t="s">
-        <v>791</v>
+        <v>659</v>
       </c>
       <c r="H144" s="2" t="s">
-        <v>792</v>
+        <v>781</v>
       </c>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>793</v>
+        <v>782</v>
       </c>
       <c r="B145" t="s">
-        <v>481</v>
+        <v>142</v>
       </c>
       <c r="C145" t="s">
-        <v>794</v>
+        <v>247</v>
       </c>
       <c r="D145" t="s">
-        <v>144</v>
+        <v>162</v>
       </c>
       <c r="E145" t="s">
-        <v>795</v>
+        <v>783</v>
       </c>
       <c r="F145" t="s">
-        <v>484</v>
+        <v>146</v>
       </c>
       <c r="H145" s="2" t="s">
-        <v>796</v>
+        <v>784</v>
       </c>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>797</v>
+        <v>785</v>
       </c>
       <c r="B146" t="s">
-        <v>798</v>
+        <v>786</v>
       </c>
       <c r="C146" t="s">
-        <v>707</v>
+        <v>787</v>
       </c>
       <c r="D146" t="s">
         <v>144</v>
       </c>
       <c r="E146" t="s">
-        <v>564</v>
+        <v>788</v>
       </c>
       <c r="F146" t="s">
-        <v>600</v>
+        <v>789</v>
       </c>
       <c r="H146" s="2" t="s">
-        <v>799</v>
+        <v>790</v>
       </c>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>800</v>
+        <v>791</v>
       </c>
       <c r="B147" t="s">
-        <v>801</v>
+        <v>792</v>
       </c>
       <c r="C147" t="s">
-        <v>802</v>
+        <v>173</v>
       </c>
       <c r="D147" t="s">
         <v>144</v>
       </c>
       <c r="E147" t="s">
-        <v>803</v>
+        <v>654</v>
       </c>
       <c r="F147" t="s">
-        <v>804</v>
+        <v>793</v>
       </c>
       <c r="H147" s="2" t="s">
-        <v>805</v>
+        <v>794</v>
       </c>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>800</v>
+        <v>795</v>
       </c>
       <c r="B148" t="s">
-        <v>806</v>
+        <v>796</v>
       </c>
       <c r="C148" t="s">
         <v>173</v>
@@ -7090,404 +7192,657 @@
         <v>370</v>
       </c>
       <c r="E148" t="s">
-        <v>647</v>
+        <v>797</v>
       </c>
       <c r="F148" t="s">
-        <v>407</v>
+        <v>138</v>
       </c>
       <c r="H148" s="2" t="s">
-        <v>807</v>
+        <v>798</v>
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>808</v>
+        <v>799</v>
       </c>
       <c r="B149" t="s">
-        <v>809</v>
+        <v>800</v>
       </c>
       <c r="C149" t="s">
-        <v>810</v>
+        <v>247</v>
       </c>
       <c r="D149" t="s">
-        <v>144</v>
+        <v>168</v>
       </c>
       <c r="E149" t="s">
-        <v>811</v>
+        <v>801</v>
       </c>
       <c r="F149" t="s">
-        <v>812</v>
+        <v>802</v>
       </c>
       <c r="H149" s="2" t="s">
-        <v>813</v>
+        <v>803</v>
       </c>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>814</v>
+        <v>804</v>
       </c>
       <c r="B150" t="s">
-        <v>815</v>
+        <v>751</v>
       </c>
       <c r="C150" t="s">
-        <v>757</v>
+        <v>752</v>
       </c>
       <c r="D150" t="s">
         <v>144</v>
       </c>
       <c r="E150" t="s">
-        <v>816</v>
+        <v>805</v>
       </c>
       <c r="F150" t="s">
-        <v>817</v>
+        <v>753</v>
       </c>
       <c r="H150" s="2" t="s">
-        <v>818</v>
+        <v>806</v>
       </c>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>819</v>
+        <v>807</v>
       </c>
       <c r="B151" t="s">
-        <v>820</v>
+        <v>501</v>
       </c>
       <c r="C151" t="s">
-        <v>821</v>
+        <v>808</v>
       </c>
       <c r="D151" t="s">
         <v>144</v>
       </c>
       <c r="E151" t="s">
-        <v>822</v>
+        <v>809</v>
       </c>
       <c r="F151" t="s">
-        <v>823</v>
+        <v>504</v>
       </c>
       <c r="H151" s="2" t="s">
-        <v>824</v>
+        <v>810</v>
       </c>
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>825</v>
+        <v>811</v>
       </c>
       <c r="B152" t="s">
-        <v>826</v>
+        <v>812</v>
       </c>
       <c r="C152" t="s">
-        <v>472</v>
+        <v>813</v>
       </c>
       <c r="D152" t="s">
         <v>144</v>
       </c>
       <c r="E152" t="s">
-        <v>827</v>
+        <v>814</v>
       </c>
       <c r="F152" t="s">
-        <v>828</v>
+        <v>815</v>
       </c>
       <c r="H152" s="2" t="s">
-        <v>829</v>
+        <v>816</v>
       </c>
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>830</v>
+        <v>817</v>
       </c>
       <c r="B153" t="s">
-        <v>831</v>
+        <v>756</v>
       </c>
       <c r="C153" t="s">
-        <v>219</v>
+        <v>359</v>
       </c>
       <c r="D153" t="s">
         <v>144</v>
       </c>
       <c r="E153" t="s">
-        <v>832</v>
+        <v>757</v>
       </c>
       <c r="F153" t="s">
-        <v>833</v>
+        <v>138</v>
       </c>
       <c r="H153" s="2" t="s">
-        <v>834</v>
+        <v>818</v>
       </c>
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>835</v>
+        <v>819</v>
       </c>
       <c r="B154" t="s">
-        <v>481</v>
+        <v>268</v>
       </c>
       <c r="C154" t="s">
-        <v>482</v>
+        <v>247</v>
       </c>
       <c r="D154" t="s">
         <v>144</v>
       </c>
       <c r="E154" t="s">
-        <v>836</v>
+        <v>820</v>
       </c>
       <c r="F154" t="s">
-        <v>484</v>
+        <v>270</v>
       </c>
       <c r="H154" s="2" t="s">
-        <v>837</v>
+        <v>821</v>
       </c>
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>838</v>
+        <v>822</v>
       </c>
       <c r="B155" t="s">
-        <v>839</v>
+        <v>823</v>
       </c>
       <c r="C155" t="s">
-        <v>314</v>
+        <v>299</v>
       </c>
       <c r="D155" t="s">
-        <v>168</v>
+        <v>144</v>
       </c>
       <c r="E155" t="s">
-        <v>840</v>
+        <v>824</v>
       </c>
       <c r="F155" t="s">
-        <v>841</v>
+        <v>825</v>
       </c>
       <c r="H155" s="2" t="s">
-        <v>842</v>
+        <v>826</v>
       </c>
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>843</v>
+        <v>827</v>
       </c>
       <c r="B156" t="s">
-        <v>528</v>
+        <v>481</v>
       </c>
       <c r="C156" t="s">
-        <v>507</v>
+        <v>828</v>
       </c>
       <c r="D156" t="s">
         <v>144</v>
       </c>
       <c r="E156" t="s">
-        <v>844</v>
+        <v>829</v>
       </c>
       <c r="F156" t="s">
-        <v>845</v>
+        <v>484</v>
       </c>
       <c r="H156" s="2" t="s">
-        <v>846</v>
+        <v>830</v>
       </c>
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>847</v>
+        <v>831</v>
       </c>
       <c r="B157" t="s">
-        <v>778</v>
+        <v>832</v>
       </c>
       <c r="C157" t="s">
-        <v>779</v>
+        <v>731</v>
       </c>
       <c r="D157" t="s">
         <v>144</v>
       </c>
       <c r="E157" t="s">
-        <v>848</v>
+        <v>579</v>
       </c>
       <c r="F157" t="s">
-        <v>781</v>
+        <v>621</v>
       </c>
       <c r="H157" s="2" t="s">
-        <v>849</v>
+        <v>833</v>
       </c>
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>850</v>
+        <v>834</v>
       </c>
       <c r="B158" t="s">
-        <v>851</v>
+        <v>835</v>
       </c>
       <c r="C158" t="s">
-        <v>247</v>
+        <v>836</v>
       </c>
       <c r="D158" t="s">
         <v>144</v>
       </c>
       <c r="E158" t="s">
-        <v>852</v>
+        <v>837</v>
       </c>
       <c r="F158" t="s">
-        <v>853</v>
+        <v>838</v>
       </c>
       <c r="H158" s="2" t="s">
-        <v>854</v>
+        <v>839</v>
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>855</v>
+        <v>834</v>
       </c>
       <c r="B159" t="s">
-        <v>856</v>
+        <v>840</v>
       </c>
       <c r="C159" t="s">
-        <v>247</v>
+        <v>173</v>
       </c>
       <c r="D159" t="s">
-        <v>144</v>
+        <v>370</v>
       </c>
       <c r="E159" t="s">
-        <v>857</v>
+        <v>670</v>
       </c>
       <c r="F159" t="s">
-        <v>858</v>
+        <v>407</v>
       </c>
       <c r="H159" s="2" t="s">
-        <v>859</v>
+        <v>841</v>
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>860</v>
+        <v>842</v>
       </c>
       <c r="B160" t="s">
-        <v>861</v>
+        <v>843</v>
       </c>
       <c r="C160" t="s">
-        <v>247</v>
+        <v>844</v>
       </c>
       <c r="D160" t="s">
         <v>144</v>
       </c>
       <c r="E160" t="s">
-        <v>138</v>
+        <v>845</v>
       </c>
       <c r="F160" t="s">
-        <v>812</v>
+        <v>846</v>
       </c>
       <c r="H160" s="2" t="s">
-        <v>862</v>
+        <v>847</v>
       </c>
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>863</v>
+        <v>848</v>
       </c>
       <c r="B161" t="s">
-        <v>481</v>
+        <v>849</v>
       </c>
       <c r="C161" t="s">
-        <v>482</v>
+        <v>787</v>
       </c>
       <c r="D161" t="s">
         <v>144</v>
       </c>
       <c r="E161" t="s">
-        <v>864</v>
+        <v>850</v>
       </c>
       <c r="F161" t="s">
-        <v>484</v>
+        <v>851</v>
       </c>
       <c r="H161" s="2" t="s">
-        <v>865</v>
+        <v>852</v>
       </c>
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>866</v>
+        <v>853</v>
       </c>
       <c r="B162" t="s">
-        <v>405</v>
+        <v>854</v>
       </c>
       <c r="C162" t="s">
-        <v>173</v>
+        <v>855</v>
       </c>
       <c r="D162" t="s">
         <v>144</v>
       </c>
       <c r="E162" t="s">
-        <v>867</v>
+        <v>856</v>
       </c>
       <c r="F162" t="s">
-        <v>407</v>
+        <v>857</v>
       </c>
       <c r="H162" s="2" t="s">
-        <v>868</v>
+        <v>858</v>
       </c>
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>869</v>
+        <v>859</v>
       </c>
       <c r="B163" t="s">
-        <v>405</v>
+        <v>860</v>
       </c>
       <c r="C163" t="s">
-        <v>173</v>
+        <v>472</v>
       </c>
       <c r="D163" t="s">
         <v>144</v>
       </c>
       <c r="E163" t="s">
-        <v>867</v>
+        <v>861</v>
       </c>
       <c r="F163" t="s">
-        <v>407</v>
+        <v>862</v>
       </c>
       <c r="H163" s="2" t="s">
-        <v>870</v>
+        <v>863</v>
       </c>
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>871</v>
+        <v>864</v>
       </c>
       <c r="B164" t="s">
-        <v>872</v>
+        <v>865</v>
       </c>
       <c r="C164" t="s">
-        <v>173</v>
+        <v>219</v>
       </c>
       <c r="D164" t="s">
-        <v>202</v>
+        <v>144</v>
       </c>
       <c r="E164" t="s">
-        <v>203</v>
+        <v>866</v>
       </c>
       <c r="F164" t="s">
-        <v>281</v>
+        <v>867</v>
       </c>
       <c r="H164" s="2" t="s">
-        <v>873</v>
+        <v>868</v>
       </c>
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
+        <v>869</v>
+      </c>
+      <c r="B165" t="s">
+        <v>481</v>
+      </c>
+      <c r="C165" t="s">
+        <v>482</v>
+      </c>
+      <c r="D165" t="s">
+        <v>144</v>
+      </c>
+      <c r="E165" t="s">
+        <v>870</v>
+      </c>
+      <c r="F165" t="s">
+        <v>484</v>
+      </c>
+      <c r="H165" s="2" t="s">
+        <v>871</v>
+      </c>
+    </row>
+    <row r="166" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
+        <v>872</v>
+      </c>
+      <c r="B166" t="s">
+        <v>873</v>
+      </c>
+      <c r="C166" t="s">
+        <v>314</v>
+      </c>
+      <c r="D166" t="s">
+        <v>168</v>
+      </c>
+      <c r="E166" t="s">
         <v>874</v>
       </c>
-      <c r="B165" t="s">
+      <c r="F166" t="s">
+        <v>875</v>
+      </c>
+      <c r="H166" s="2" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="167" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
+        <v>877</v>
+      </c>
+      <c r="B167" t="s">
+        <v>534</v>
+      </c>
+      <c r="C167" t="s">
+        <v>513</v>
+      </c>
+      <c r="D167" t="s">
+        <v>144</v>
+      </c>
+      <c r="E167" t="s">
+        <v>878</v>
+      </c>
+      <c r="F167" t="s">
+        <v>879</v>
+      </c>
+      <c r="H167" s="2" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="168" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>881</v>
+      </c>
+      <c r="B168" t="s">
+        <v>812</v>
+      </c>
+      <c r="C168" t="s">
+        <v>813</v>
+      </c>
+      <c r="D168" t="s">
+        <v>144</v>
+      </c>
+      <c r="E168" t="s">
+        <v>882</v>
+      </c>
+      <c r="F168" t="s">
+        <v>815</v>
+      </c>
+      <c r="H168" s="2" t="s">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="169" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
+        <v>884</v>
+      </c>
+      <c r="B169" t="s">
+        <v>885</v>
+      </c>
+      <c r="C169" t="s">
+        <v>247</v>
+      </c>
+      <c r="D169" t="s">
+        <v>144</v>
+      </c>
+      <c r="E169" t="s">
+        <v>886</v>
+      </c>
+      <c r="F169" t="s">
+        <v>887</v>
+      </c>
+      <c r="H169" s="2" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="170" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
+        <v>889</v>
+      </c>
+      <c r="B170" t="s">
+        <v>890</v>
+      </c>
+      <c r="C170" t="s">
+        <v>247</v>
+      </c>
+      <c r="D170" t="s">
+        <v>144</v>
+      </c>
+      <c r="E170" t="s">
+        <v>891</v>
+      </c>
+      <c r="F170" t="s">
+        <v>892</v>
+      </c>
+      <c r="H170" s="2" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="171" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
+        <v>894</v>
+      </c>
+      <c r="B171" t="s">
+        <v>895</v>
+      </c>
+      <c r="C171" t="s">
+        <v>247</v>
+      </c>
+      <c r="D171" t="s">
+        <v>144</v>
+      </c>
+      <c r="E171" t="s">
+        <v>138</v>
+      </c>
+      <c r="F171" t="s">
+        <v>846</v>
+      </c>
+      <c r="H171" s="2" t="s">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="172" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
+        <v>897</v>
+      </c>
+      <c r="B172" t="s">
+        <v>481</v>
+      </c>
+      <c r="C172" t="s">
+        <v>482</v>
+      </c>
+      <c r="D172" t="s">
+        <v>144</v>
+      </c>
+      <c r="E172" t="s">
+        <v>898</v>
+      </c>
+      <c r="F172" t="s">
+        <v>484</v>
+      </c>
+      <c r="H172" s="2" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="173" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A173" t="s">
+        <v>900</v>
+      </c>
+      <c r="B173" t="s">
+        <v>405</v>
+      </c>
+      <c r="C173" t="s">
+        <v>173</v>
+      </c>
+      <c r="D173" t="s">
+        <v>144</v>
+      </c>
+      <c r="E173" t="s">
+        <v>901</v>
+      </c>
+      <c r="F173" t="s">
+        <v>407</v>
+      </c>
+      <c r="H173" s="2" t="s">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="174" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
+        <v>903</v>
+      </c>
+      <c r="B174" t="s">
+        <v>405</v>
+      </c>
+      <c r="C174" t="s">
+        <v>173</v>
+      </c>
+      <c r="D174" t="s">
+        <v>144</v>
+      </c>
+      <c r="E174" t="s">
+        <v>901</v>
+      </c>
+      <c r="F174" t="s">
+        <v>407</v>
+      </c>
+      <c r="H174" s="2" t="s">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="175" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
+        <v>905</v>
+      </c>
+      <c r="B175" t="s">
+        <v>906</v>
+      </c>
+      <c r="C175" t="s">
+        <v>173</v>
+      </c>
+      <c r="D175" t="s">
+        <v>202</v>
+      </c>
+      <c r="E175" t="s">
+        <v>203</v>
+      </c>
+      <c r="F175" t="s">
+        <v>281</v>
+      </c>
+      <c r="H175" s="2" t="s">
+        <v>907</v>
+      </c>
+    </row>
+    <row r="176" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A176" t="s">
+        <v>908</v>
+      </c>
+      <c r="B176" t="s">
         <v>209</v>
       </c>
-      <c r="C165" t="s">
+      <c r="C176" t="s">
         <v>210</v>
       </c>
-      <c r="D165" t="s">
+      <c r="D176" t="s">
         <v>162</v>
       </c>
-      <c r="E165" t="s">
+      <c r="E176" t="s">
         <v>138</v>
       </c>
-      <c r="F165" t="s">
+      <c r="F176" t="s">
         <v>215</v>
       </c>
-      <c r="H165" s="2" t="s">
-        <v>875</v>
+      <c r="H176" s="2" t="s">
+        <v>909</v>
       </c>
     </row>
   </sheetData>
@@ -7657,6 +8012,17 @@
     <hyperlink ref="H163" r:id="rId162"/>
     <hyperlink ref="H164" r:id="rId163"/>
     <hyperlink ref="H165" r:id="rId164"/>
+    <hyperlink ref="H166" r:id="rId165"/>
+    <hyperlink ref="H167" r:id="rId166"/>
+    <hyperlink ref="H168" r:id="rId167"/>
+    <hyperlink ref="H169" r:id="rId168"/>
+    <hyperlink ref="H170" r:id="rId169"/>
+    <hyperlink ref="H171" r:id="rId170"/>
+    <hyperlink ref="H172" r:id="rId171"/>
+    <hyperlink ref="H173" r:id="rId172"/>
+    <hyperlink ref="H174" r:id="rId173"/>
+    <hyperlink ref="H175" r:id="rId174"/>
+    <hyperlink ref="H176" r:id="rId175"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
